--- a/Results/Phase 2/Hydrogen/hydrogen water use results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen water use results.xlsx
@@ -886,7 +886,7 @@
         <v>0.1353797884942224</v>
       </c>
       <c r="N5" t="n">
-        <v>3.184022531470438</v>
+        <v>0.1353797884942223</v>
       </c>
       <c r="O5" t="n">
         <v>0.1353797884942223</v>
@@ -974,7 +974,7 @@
         <v>88.02151008726376</v>
       </c>
       <c r="N6" t="n">
-        <v>3.184022531470438</v>
+        <v>7.270142241574338</v>
       </c>
       <c r="O6" t="n">
         <v>7.270142585604866</v>
@@ -1062,7 +1062,7 @@
         <v>0.5366761637661062</v>
       </c>
       <c r="N7" t="n">
-        <v>3.184022531470438</v>
+        <v>0.5366761637661062</v>
       </c>
       <c r="O7" t="n">
         <v>0.5366474939824565</v>
@@ -1150,7 +1150,7 @@
         <v>0.9256652461990635</v>
       </c>
       <c r="N8" t="n">
-        <v>3.184022531470438</v>
+        <v>0.6722535227914775</v>
       </c>
       <c r="O8" t="n">
         <v>0.7418932647010537</v>
@@ -1238,7 +1238,7 @@
         <v>4.613699270117313</v>
       </c>
       <c r="N9" t="n">
-        <v>3.184022531470438</v>
+        <v>4.613699270117313</v>
       </c>
       <c r="O9" t="n">
         <v>4.93889049068907</v>
@@ -1682,7 +1682,7 @@
         <v>0.2159086790503656</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2507430872426782</v>
+        <v>0.2507430872426783</v>
       </c>
       <c r="W2" t="n">
         <v>0.2057084571343954</v>
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="E3" t="n">
         <v>0.1569587768180553</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="J3" t="n">
         <v>0.1875217126472724</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="V3" t="n">
         <v>0.2241549721041015</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1873389371525</v>
+        <v>0.1873389371525001</v>
       </c>
     </row>
     <row r="4">
@@ -1922,7 +1922,7 @@
         <v>0.1148570082228506</v>
       </c>
       <c r="N5" t="n">
-        <v>2.122822966128358</v>
+        <v>0.1148570082228503</v>
       </c>
       <c r="O5" t="n">
         <v>0.1148570082228503</v>
@@ -2010,7 +2010,7 @@
         <v>6.323032429908896</v>
       </c>
       <c r="N6" t="n">
-        <v>2.122822966128358</v>
+        <v>6.315614189139267</v>
       </c>
       <c r="O6" t="n">
         <v>76.70375170880342</v>
@@ -2098,7 +2098,7 @@
         <v>0.4568954431495667</v>
       </c>
       <c r="N7" t="n">
-        <v>2.122822966128358</v>
+        <v>0.4568954431495667</v>
       </c>
       <c r="O7" t="n">
         <v>0.4568704530432617</v>
@@ -2186,7 +2186,7 @@
         <v>0.7839740862891313</v>
       </c>
       <c r="N8" t="n">
-        <v>2.122822966128358</v>
+        <v>0.5694425173149754</v>
       </c>
       <c r="O8" t="n">
         <v>0.6283976551954545</v>
@@ -2274,7 +2274,7 @@
         <v>2.814105941719205</v>
       </c>
       <c r="N9" t="n">
-        <v>2.122822966128358</v>
+        <v>2.814105941719205</v>
       </c>
       <c r="O9" t="n">
         <v>3.010999811788023</v>
@@ -2353,7 +2353,7 @@
         <v>-0.009377260565933986</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.05660582334644759</v>
+        <v>-0.05660582334644758</v>
       </c>
       <c r="L10" t="n">
         <v>-0.1558155486991683</v>
@@ -2389,7 +2389,7 @@
         <v>0.05441128020948906</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0705060956830135</v>
+        <v>0.07050609568301351</v>
       </c>
       <c r="X10" t="n">
         <v>-0.1157981200793693</v>
@@ -2423,7 +2423,7 @@
         <v>0.1259031116258414</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.03738869482551668</v>
+        <v>-0.03738869482551669</v>
       </c>
       <c r="F11" t="n">
         <v>-0.1365900095391384</v>
@@ -2447,7 +2447,7 @@
         <v>0.08782178411388417</v>
       </c>
       <c r="M11" t="n">
-        <v>0.102485844329263</v>
+        <v>0.1024858443292631</v>
       </c>
       <c r="N11" t="n">
         <v>0.1731656854731183</v>
@@ -2958,7 +2958,7 @@
         <v>0.1351291127621927</v>
       </c>
       <c r="N5" t="n">
-        <v>2.895763566501037</v>
+        <v>0.1351291127621922</v>
       </c>
       <c r="O5" t="n">
         <v>0.1351291127621922</v>
@@ -3046,7 +3046,7 @@
         <v>82.37223341858376</v>
       </c>
       <c r="N6" t="n">
-        <v>2.895763566501037</v>
+        <v>6.809662289426058</v>
       </c>
       <c r="O6" t="n">
         <v>6.809652333068236</v>
@@ -3134,7 +3134,7 @@
         <v>0.5121924037037006</v>
       </c>
       <c r="N7" t="n">
-        <v>2.895763566501037</v>
+        <v>0.5121924037037006</v>
       </c>
       <c r="O7" t="n">
         <v>0.5121653239940132</v>
@@ -3222,7 +3222,7 @@
         <v>0.8809375182946465</v>
       </c>
       <c r="N8" t="n">
-        <v>2.895763566501037</v>
+        <v>0.6417514011353105</v>
       </c>
       <c r="O8" t="n">
         <v>0.7074818229284933</v>
@@ -3310,7 +3310,7 @@
         <v>3.819349540753902</v>
       </c>
       <c r="N9" t="n">
-        <v>2.895763566501037</v>
+        <v>3.819349540753902</v>
       </c>
       <c r="O9" t="n">
         <v>4.087330601875785</v>
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2057364986957498</v>
+        <v>0.2057364986957491</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3489674397838795</v>
+        <v>0.3489674397838792</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2755397362205886</v>
+        <v>0.2755397362205885</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2920091013157562</v>
+        <v>0.2920091013157563</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3834546949446048</v>
+        <v>0.3834546949446044</v>
       </c>
       <c r="G2" t="n">
         <v>0.2162181520798264</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2249935988273192</v>
+        <v>0.2249935988273189</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2498347327052116</v>
+        <v>0.2498347327052112</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2319384571857377</v>
+        <v>0.2319384571857371</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2392442443802603</v>
+        <v>0.2392442443802602</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2477901009897558</v>
+        <v>0.2477901009897556</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2292941748927846</v>
+        <v>0.229294174892784</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2050618839099858</v>
+        <v>0.2050618839099856</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2215378160743196</v>
+        <v>0.2215378160743192</v>
       </c>
       <c r="P2" t="n">
-        <v>0.227244192939269</v>
+        <v>0.2272441929392688</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2061383776796328</v>
+        <v>0.2061383776796326</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2716488035186413</v>
+        <v>0.2716488035186412</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2458162705525955</v>
+        <v>0.245816270552595</v>
       </c>
       <c r="T2" t="n">
-        <v>0.213534276183613</v>
+        <v>0.2135342761836122</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2278815164886977</v>
+        <v>0.2278815164886978</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2774831629783528</v>
+        <v>0.2774831629783531</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2219281962897273</v>
+        <v>0.2219281962897271</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2461191598344231</v>
+        <v>0.2461191598344232</v>
       </c>
       <c r="Y2" t="n">
         <v>0.2161398800948547</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2133630349185322</v>
+        <v>0.2133630349185321</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2448537700639766</v>
+        <v>0.2448537700639765</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2150228750869</v>
+        <v>0.2150228750868999</v>
       </c>
     </row>
     <row r="3">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="E3" t="n">
         <v>0.1668585234218752</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1983888092380742</v>
+        <v>0.1983888092380743</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2389131503051229</v>
+        <v>0.2389131503051231</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1980463244144169</v>
+        <v>0.1980463244144167</v>
       </c>
     </row>
     <row r="4">
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.369067877068469</v>
+        <v>2.369067877068482</v>
       </c>
       <c r="C4" t="n">
-        <v>37.60962010785786</v>
+        <v>37.60962010785782</v>
       </c>
       <c r="D4" t="n">
         <v>20.91824698787184</v>
       </c>
       <c r="E4" t="n">
-        <v>31.93592028076039</v>
+        <v>31.93592028076036</v>
       </c>
       <c r="F4" t="n">
-        <v>48.79531580806319</v>
+        <v>48.79531580806316</v>
       </c>
       <c r="G4" t="n">
-        <v>4.835367328225761</v>
+        <v>4.835367328225803</v>
       </c>
       <c r="H4" t="n">
-        <v>8.037336020978664</v>
+        <v>8.037336020978671</v>
       </c>
       <c r="I4" t="n">
-        <v>14.40213728324734</v>
+        <v>14.4021372832473</v>
       </c>
       <c r="J4" t="n">
-        <v>8.866134396091747</v>
+        <v>8.866134396091752</v>
       </c>
       <c r="K4" t="n">
-        <v>10.21946146055982</v>
+        <v>10.21946146055981</v>
       </c>
       <c r="L4" t="n">
-        <v>13.00422565061851</v>
+        <v>13.0042256506185</v>
       </c>
       <c r="M4" t="n">
-        <v>8.924830176907967</v>
+        <v>8.924830176907943</v>
       </c>
       <c r="N4" t="n">
-        <v>2.371762749345291</v>
+        <v>2.371762749345289</v>
       </c>
       <c r="O4" t="n">
-        <v>5.835660041682079</v>
+        <v>5.835660041682091</v>
       </c>
       <c r="P4" t="n">
-        <v>7.41788608655996</v>
+        <v>7.417886086559956</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.617525759513482</v>
+        <v>2.617525759513474</v>
       </c>
       <c r="R4" t="n">
         <v>20.55844571975665</v>
       </c>
       <c r="S4" t="n">
-        <v>11.87843648749995</v>
+        <v>11.87843648749994</v>
       </c>
       <c r="T4" t="n">
-        <v>4.682681499992393</v>
+        <v>4.682681499992392</v>
       </c>
       <c r="U4" t="n">
-        <v>7.811678258578858</v>
+        <v>7.811678258578977</v>
       </c>
       <c r="V4" t="n">
-        <v>9.355646168771399</v>
+        <v>9.355646168771427</v>
       </c>
       <c r="W4" t="n">
-        <v>6.61029792026664</v>
+        <v>6.610297920266629</v>
       </c>
       <c r="X4" t="n">
-        <v>13.01752415599075</v>
+        <v>13.01752415599076</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.112889507983086</v>
+        <v>5.112889507983088</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.006361642765723</v>
+        <v>4.006361642765712</v>
       </c>
       <c r="AA4" t="n">
         <v>12.43300331840452</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.342392610465986</v>
+        <v>5.342392610465981</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1284258700423946</v>
+        <v>0.1284258700423939</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1284258700423948</v>
+        <v>0.1284258700423936</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1284258700423948</v>
+        <v>0.1284258700423936</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1284258700423948</v>
+        <v>0.1284258700423936</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1284258700423947</v>
+        <v>0.1284258700423938</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1284258700423948</v>
+        <v>0.1284258700423936</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1284258700423948</v>
+        <v>0.1284258700423936</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1284258700423948</v>
+        <v>0.1284258700423936</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1286169393345512</v>
+        <v>0.1286169393345504</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1284258700423948</v>
+        <v>0.1284258700423936</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1284258700423948</v>
+        <v>0.1284258700423937</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1284258700423948</v>
+        <v>0.1284258700423936</v>
       </c>
       <c r="N5" t="n">
-        <v>2.371762749345291</v>
+        <v>0.1284258700423938</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1284258700423947</v>
+        <v>0.1284258700423938</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1284258700423947</v>
+        <v>0.1284258700423938</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1284258700423947</v>
+        <v>0.1284258700423938</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1284258700423948</v>
+        <v>0.1284258700423936</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1284258700423948</v>
+        <v>0.1284258700423936</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1284258700423948</v>
+        <v>0.1284258700423936</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1304913819755397</v>
+        <v>0.1304913819755387</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1292230587121162</v>
+        <v>0.1292230587121161</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1284258700423947</v>
+        <v>0.1284258700423938</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1284258700423946</v>
+        <v>0.1284258700423939</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1304913819755397</v>
+        <v>0.1304913819755387</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1284258700423948</v>
+        <v>0.1284258700423936</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1284258700423948</v>
+        <v>0.1284258700423936</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1284258700423947</v>
+        <v>0.1284258700423938</v>
       </c>
     </row>
     <row r="6">
@@ -4046,64 +4046,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>76.74346306267148</v>
+        <v>76.74346306267152</v>
       </c>
       <c r="C6" t="n">
-        <v>6.347867628056663</v>
+        <v>6.347867628056656</v>
       </c>
       <c r="D6" t="n">
-        <v>76.74346306267147</v>
+        <v>76.74346306267149</v>
       </c>
       <c r="E6" t="n">
-        <v>76.74346306267147</v>
+        <v>76.74346306267149</v>
       </c>
       <c r="F6" t="n">
-        <v>6.347867628056663</v>
+        <v>6.347867628056656</v>
       </c>
       <c r="G6" t="n">
-        <v>6.347867628056663</v>
+        <v>6.347867628056656</v>
       </c>
       <c r="H6" t="n">
-        <v>6.347867628056663</v>
+        <v>6.347867628056656</v>
       </c>
       <c r="I6" t="n">
-        <v>6.347867628056663</v>
+        <v>6.347867628056656</v>
       </c>
       <c r="J6" t="n">
-        <v>76.74365413196351</v>
+        <v>76.74365413196354</v>
       </c>
       <c r="K6" t="n">
-        <v>76.74346306267147</v>
+        <v>76.74346306267149</v>
       </c>
       <c r="L6" t="n">
-        <v>76.74346306267148</v>
+        <v>76.74346306267152</v>
       </c>
       <c r="M6" t="n">
-        <v>6.347867628056663</v>
+        <v>6.347867628056656</v>
       </c>
       <c r="N6" t="n">
-        <v>2.371762749345291</v>
+        <v>6.340261909624066</v>
       </c>
       <c r="O6" t="n">
-        <v>76.73883686775562</v>
+        <v>76.73883686775561</v>
       </c>
       <c r="P6" t="n">
         <v>76.73885277850034</v>
       </c>
       <c r="Q6" t="n">
-        <v>76.74346306267147</v>
+        <v>76.74346306267149</v>
       </c>
       <c r="R6" t="n">
-        <v>6.347867628056663</v>
+        <v>6.347867628056656</v>
       </c>
       <c r="S6" t="n">
-        <v>76.74346306267147</v>
+        <v>76.74346306267149</v>
       </c>
       <c r="T6" t="n">
-        <v>6.347867628056663</v>
+        <v>6.347867628056656</v>
       </c>
       <c r="U6" t="n">
-        <v>6.347867628056663</v>
+        <v>6.347867628056656</v>
       </c>
       <c r="V6" t="n">
         <v>76.7442602513412</v>
@@ -4112,16 +4112,16 @@
         <v>76.73882963806919</v>
       </c>
       <c r="X6" t="n">
-        <v>6.347867628056663</v>
+        <v>6.347867628056656</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.444682422606667</v>
+        <v>6.44468242260667</v>
       </c>
       <c r="Z6" t="n">
-        <v>76.74346306267147</v>
+        <v>76.74346306267149</v>
       </c>
       <c r="AA6" t="n">
-        <v>76.74346306267147</v>
+        <v>76.74346306267149</v>
       </c>
       <c r="AB6" t="n">
         <v>6.338914104379388</v>
@@ -4137,82 +4137,82 @@
         <v>0.4763913747510541</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4765824440432124</v>
+        <v>0.476582444043211</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="L7" t="n">
         <v>0.4763913747510541</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="N7" t="n">
-        <v>2.371762749345291</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4763660272658365</v>
+        <v>0.4763660272658359</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4763660272658365</v>
+        <v>0.4763660272658359</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4764533875943361</v>
+        <v>0.4764533875943356</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4771885634207757</v>
+        <v>0.477188563420776</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="X7" t="n">
         <v>0.4763913747510541</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.4763913747510537</v>
+        <v>0.4763913747510539</v>
       </c>
     </row>
     <row r="8">
@@ -4225,82 +4225,82 @@
         <v>0.5290484815839148</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8121093857211125</v>
+        <v>0.8121093857211116</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8121093857211125</v>
+        <v>0.8121093857211116</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6613878040517125</v>
+        <v>0.6613878040517115</v>
       </c>
       <c r="F8" t="n">
-        <v>0.573146062241699</v>
+        <v>0.5731460622416975</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8708039081611697</v>
+        <v>0.8708039081611684</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8121093857211125</v>
+        <v>0.8121093857211116</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8121093857211125</v>
+        <v>0.8121093857211116</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8123004550132688</v>
+        <v>0.812300455013269</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8121093857211125</v>
+        <v>0.8121093857211116</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8121093857211126</v>
+        <v>0.8121093857211119</v>
       </c>
       <c r="M8" t="n">
-        <v>0.812109385721005</v>
+        <v>0.8121093857210039</v>
       </c>
       <c r="N8" t="n">
-        <v>2.371762749345291</v>
+        <v>0.5926898299471089</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6529882290408654</v>
+        <v>0.6529882290408662</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6382076344117157</v>
+        <v>0.6382076344117158</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4734205533832468</v>
+        <v>0.4734205533832466</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8121093857211125</v>
+        <v>0.8121093857211116</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8121093857211125</v>
+        <v>0.8121093857211116</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8121093857211125</v>
+        <v>0.8121093857211116</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6740188384691619</v>
+        <v>0.6740188384691623</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7356164346703995</v>
+        <v>0.7356164346703989</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8121650152585859</v>
+        <v>0.8121650152585864</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4993636476726992</v>
+        <v>0.4993636476726998</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.093666218422091</v>
+        <v>1.093666218422092</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5237904799701849</v>
+        <v>0.5237904799701847</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8121093857211125</v>
+        <v>0.8121093857211116</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.107790169220686</v>
+        <v>1.107790169220688</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.503508417885572</v>
+        <v>2.503508417885571</v>
       </c>
       <c r="C9" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="D9" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="E9" t="n">
         <v>3.018298389711826</v>
       </c>
       <c r="F9" t="n">
-        <v>1.62995427125962</v>
+        <v>1.629954271259619</v>
       </c>
       <c r="G9" t="n">
-        <v>3.172758602498861</v>
+        <v>3.172758602498857</v>
       </c>
       <c r="H9" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="I9" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="J9" t="n">
         <v>3.17294965588641</v>
       </c>
       <c r="K9" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="L9" t="n">
-        <v>3.172758586594249</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="M9" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="N9" t="n">
-        <v>2.371762749345291</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="O9" t="n">
-        <v>3.394547237372279</v>
+        <v>3.394547237372278</v>
       </c>
       <c r="P9" t="n">
-        <v>3.442782460203674</v>
+        <v>3.442782460203675</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.172758602498861</v>
+        <v>3.172758602498857</v>
       </c>
       <c r="R9" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="S9" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="T9" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="U9" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="V9" t="n">
-        <v>3.945855723497017</v>
+        <v>3.945855723497018</v>
       </c>
       <c r="W9" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="X9" t="n">
-        <v>3.172758586594249</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.769260253225696</v>
+        <v>2.769260253225694</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
     </row>
     <row r="10">
@@ -4398,85 +4398,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.143309523682233</v>
+        <v>0.1433095236822323</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.6958603430910324</v>
+        <v>-0.6958603430910317</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2647196033869594</v>
+        <v>-0.2647196033869596</v>
       </c>
       <c r="E10" t="n">
         <v>-0.5792477385622625</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8914914027107084</v>
+        <v>-0.8914914027107086</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08101753914512801</v>
+        <v>0.08101753914512606</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0324811623837981</v>
+        <v>0.03248116238379804</v>
       </c>
       <c r="I10" t="n">
         <v>-0.1135670402527489</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.008232746839727639</v>
+        <v>-0.008232746839726541</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.05247249428355329</v>
+        <v>-0.05247249428355351</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1049601410275975</v>
+        <v>-0.1049601410275971</v>
       </c>
       <c r="M10" t="n">
         <v>0.006893984883930455</v>
       </c>
       <c r="N10" t="n">
-        <v>0.147894716515942</v>
+        <v>0.1478947165159418</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04914260768798018</v>
+        <v>0.04914260768797974</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01499481658728379</v>
+        <v>0.01499481658728322</v>
       </c>
       <c r="Q10" t="n">
         <v>0.1416568222986244</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.240194113182098</v>
+        <v>-0.2401941131820981</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.09422634162257086</v>
+        <v>-0.09422634162257174</v>
       </c>
       <c r="T10" t="n">
-        <v>0.09854265023321188</v>
+        <v>0.09854265023321142</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01255105489634946</v>
+        <v>0.01255105489634842</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.002827696026036541</v>
+        <v>-0.002827696026036296</v>
       </c>
       <c r="W10" t="n">
-        <v>0.04818199228869782</v>
+        <v>0.04818199228869796</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.09266725038255447</v>
+        <v>-0.09266725038255405</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.08253157739441445</v>
+        <v>0.08253157739441397</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.09804900999462259</v>
+        <v>0.09804900999462267</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.0868922676944469</v>
+        <v>-0.0868922676944468</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.08978452137307072</v>
+        <v>0.08978452137307055</v>
       </c>
     </row>
     <row r="11">
@@ -4486,40 +4486,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1808310799267722</v>
+        <v>0.1808310799267721</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.05776294264262295</v>
+        <v>-0.0577629426426229</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06497976432345326</v>
+        <v>0.06497976432345302</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.04747162558660402</v>
+        <v>-0.04747162558660425</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1122884430480477</v>
+        <v>-0.1122884430480481</v>
       </c>
       <c r="G11" t="n">
         <v>0.1629696818336899</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1496609224785226</v>
+        <v>0.1496609224785224</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1080496587287801</v>
+        <v>0.1080496587287797</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1379249907065078</v>
+        <v>0.1379249907065079</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1252573835165781</v>
+        <v>0.1252573835165778</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1099211935893283</v>
+        <v>0.1099211935893284</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1423192512400516</v>
+        <v>0.142319251240051</v>
       </c>
       <c r="N11" t="n">
         <v>0.182242742492488</v>
@@ -4528,43 +4528,43 @@
         <v>0.1537861504358018</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1439551735273806</v>
+        <v>0.1439551735273801</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1804809745142664</v>
+        <v>0.1804809745142662</v>
       </c>
       <c r="R11" t="n">
         <v>0.07224800782281818</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1128312760880441</v>
+        <v>0.1128312760880438</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1682597873317693</v>
+        <v>0.1682597873317686</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1434805777196275</v>
+        <v>0.1434805777196276</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1674903075153069</v>
+        <v>0.1674903075153075</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1537394475832357</v>
+        <v>0.1537394475832354</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1138435568526084</v>
+        <v>0.1138435568526083</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1635803020770972</v>
+        <v>0.1635803020770969</v>
       </c>
       <c r="Z11" t="n">
         <v>0.1678639381849931</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.1152058026090281</v>
+        <v>0.115205802609028</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.165763409693192</v>
+        <v>0.1657634096931919</v>
       </c>
     </row>
   </sheetData>
@@ -4733,82 +4733,82 @@
         <v>0.1998047942421831</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3477434213967876</v>
+        <v>0.3477434213967874</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2539895969842954</v>
+        <v>0.2539895969842957</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2727388747624133</v>
+        <v>0.2727388747624138</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3562628828792321</v>
+        <v>0.3562628828792314</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2090418874766372</v>
+        <v>0.2090418874766375</v>
       </c>
       <c r="H2" t="n">
         <v>0.2152755735551673</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2268614232079882</v>
+        <v>0.2268614232079884</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2247694535739844</v>
+        <v>0.2247694535739839</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2259500859849944</v>
+        <v>0.2259500859849942</v>
       </c>
       <c r="L2" t="n">
-        <v>0.241999943592599</v>
+        <v>0.2419999435925989</v>
       </c>
       <c r="M2" t="n">
-        <v>0.230351149614085</v>
+        <v>0.2303511496140849</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1987627370048187</v>
+        <v>0.1987627370048193</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2129127569685049</v>
+        <v>0.2129127569685048</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2164890003335287</v>
+        <v>0.2164890003335285</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2017737644536131</v>
+        <v>0.201773764453613</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2498796873530174</v>
+        <v>0.2498796873530171</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2352483101752783</v>
+        <v>0.2352483101752786</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2098314228222205</v>
+        <v>0.2098314228222202</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2131485076724799</v>
+        <v>0.2131485076724804</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2652585761839097</v>
+        <v>0.2652585761839099</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2125598157104324</v>
+        <v>0.2125598157104315</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2421291333391563</v>
+        <v>0.2421291333391559</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2070267369340489</v>
+        <v>0.2070267369340479</v>
       </c>
       <c r="Z2" t="n">
         <v>0.2042699283632675</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2298238375846786</v>
+        <v>0.2298238375846784</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2094199407975857</v>
+        <v>0.2094199407975856</v>
       </c>
     </row>
     <row r="3">
@@ -4818,85 +4818,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1589862866132455</v>
+        <v>0.1589862866132458</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1929944903290401</v>
+        <v>0.19299449032904</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2323574461600323</v>
+        <v>0.2323574461600321</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1926998960501844</v>
+        <v>0.1926998960501845</v>
       </c>
     </row>
     <row r="4">
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.170253590472163</v>
+        <v>2.170253590472172</v>
       </c>
       <c r="C4" t="n">
-        <v>38.29138649101439</v>
+        <v>38.29138649101438</v>
       </c>
       <c r="D4" t="n">
-        <v>15.95546599874055</v>
+        <v>15.95546599874067</v>
       </c>
       <c r="E4" t="n">
-        <v>27.18605134280403</v>
+        <v>27.18605134280406</v>
       </c>
       <c r="F4" t="n">
-        <v>42.71137352879278</v>
+        <v>42.71137352879274</v>
       </c>
       <c r="G4" t="n">
-        <v>4.272070349933855</v>
+        <v>4.272070349933837</v>
       </c>
       <c r="H4" t="n">
-        <v>6.829406621415447</v>
+        <v>6.829406621415443</v>
       </c>
       <c r="I4" t="n">
         <v>9.511833498956063</v>
       </c>
       <c r="J4" t="n">
-        <v>8.291077764982054</v>
+        <v>8.291077764982012</v>
       </c>
       <c r="K4" t="n">
-        <v>8.359863193490252</v>
+        <v>8.35986319349025</v>
       </c>
       <c r="L4" t="n">
-        <v>12.38419559626551</v>
+        <v>12.3841955962655</v>
       </c>
       <c r="M4" t="n">
-        <v>10.19194256091455</v>
+        <v>10.19194256091451</v>
       </c>
       <c r="N4" t="n">
-        <v>2.110777612662492</v>
+        <v>2.110777612662491</v>
       </c>
       <c r="O4" t="n">
-        <v>5.087752473452292</v>
+        <v>5.087752473452298</v>
       </c>
       <c r="P4" t="n">
-        <v>5.9396943482203</v>
+        <v>5.939694348220245</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.79034432722039</v>
+        <v>2.790344327220377</v>
       </c>
       <c r="R4" t="n">
         <v>16.0811169408567</v>
       </c>
       <c r="S4" t="n">
-        <v>10.47768539042703</v>
+        <v>10.47768539042708</v>
       </c>
       <c r="T4" t="n">
-        <v>5.104447421220357</v>
+        <v>5.104447421220362</v>
       </c>
       <c r="U4" t="n">
-        <v>5.348202375336974</v>
+        <v>5.348202375336972</v>
       </c>
       <c r="V4" t="n">
-        <v>7.991391632653579</v>
+        <v>7.991391632653545</v>
       </c>
       <c r="W4" t="n">
-        <v>5.579077054546267</v>
+        <v>5.579077054546259</v>
       </c>
       <c r="X4" t="n">
-        <v>12.93899507014302</v>
+        <v>12.93899507014297</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.208821669467206</v>
+        <v>4.208821669467115</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.017345609843375</v>
+        <v>3.017345609843377</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.01149134337635</v>
+        <v>10.01149134337634</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.183404984265538</v>
+        <v>5.183404984265529</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1222961462076344</v>
+        <v>0.1222961462076354</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1222961462076342</v>
+        <v>0.1222961462076357</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1222961462076342</v>
+        <v>0.1222961462076357</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1222961462076342</v>
+        <v>0.1222961462076357</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1222961462076343</v>
+        <v>0.1222961462076347</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1222961462076342</v>
+        <v>0.1222961462076357</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1222961462076342</v>
+        <v>0.1222961462076357</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1222961462076342</v>
+        <v>0.1222961462076357</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1224799376707712</v>
+        <v>0.1224799376707722</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1222961462076342</v>
+        <v>0.1222961462076357</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1222961462076344</v>
+        <v>0.1222961462076358</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1222961462076342</v>
+        <v>0.1222961462076357</v>
       </c>
       <c r="N5" t="n">
-        <v>2.110777612662492</v>
+        <v>0.1222961462076347</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1222961462076343</v>
+        <v>0.1222961462076347</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1222961462076343</v>
+        <v>0.1222961462076347</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1222961462076343</v>
+        <v>0.1222961462076347</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1222961462076342</v>
+        <v>0.1222961462076357</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1222961462076342</v>
+        <v>0.1222961462076357</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1222961462076342</v>
+        <v>0.1222961462076357</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1243860346299402</v>
+        <v>0.1243860346299412</v>
       </c>
       <c r="V5" t="n">
-        <v>0.123045914146036</v>
+        <v>0.1230459141460361</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1222961462076343</v>
+        <v>0.1222961462076347</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1222961462076345</v>
+        <v>0.1222961462076349</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1243860346299402</v>
+        <v>0.1243860346299412</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1222961462076342</v>
+        <v>0.1222961462076357</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1222961462076342</v>
+        <v>0.1222961462076357</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1222961462076343</v>
+        <v>0.1222961462076347</v>
       </c>
     </row>
     <row r="6">
@@ -5082,85 +5082,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.332945429990315</v>
+        <v>6.332945429990318</v>
       </c>
       <c r="C6" t="n">
-        <v>6.332945429990315</v>
+        <v>6.332945429990318</v>
       </c>
       <c r="D6" t="n">
-        <v>76.72606659875015</v>
+        <v>76.72606659875018</v>
       </c>
       <c r="E6" t="n">
-        <v>76.72606659875015</v>
+        <v>76.72606659875018</v>
       </c>
       <c r="F6" t="n">
-        <v>6.332945429990315</v>
+        <v>6.332945429990318</v>
       </c>
       <c r="G6" t="n">
-        <v>6.332945429990315</v>
+        <v>6.332945429990318</v>
       </c>
       <c r="H6" t="n">
-        <v>76.72606659875015</v>
+        <v>76.72606659875018</v>
       </c>
       <c r="I6" t="n">
-        <v>6.332945429990315</v>
+        <v>6.332945429990318</v>
       </c>
       <c r="J6" t="n">
-        <v>76.72625039021335</v>
+        <v>76.72625039021332</v>
       </c>
       <c r="K6" t="n">
-        <v>76.72606659875015</v>
+        <v>76.72606659875018</v>
       </c>
       <c r="L6" t="n">
-        <v>6.332945429990315</v>
+        <v>6.332945429990318</v>
       </c>
       <c r="M6" t="n">
-        <v>6.332945429990315</v>
+        <v>6.332945429990318</v>
       </c>
       <c r="N6" t="n">
-        <v>2.110777612662492</v>
+        <v>6.325752318639336</v>
       </c>
       <c r="O6" t="n">
-        <v>6.32574840541459</v>
+        <v>6.325748405414596</v>
       </c>
       <c r="P6" t="n">
         <v>76.72077613665071</v>
       </c>
       <c r="Q6" t="n">
-        <v>76.72606659875015</v>
+        <v>76.72606659875018</v>
       </c>
       <c r="R6" t="n">
-        <v>76.72606659875015</v>
+        <v>76.72606659875018</v>
       </c>
       <c r="S6" t="n">
-        <v>6.332945429990315</v>
+        <v>6.332945429990318</v>
       </c>
       <c r="T6" t="n">
-        <v>76.72606659875015</v>
+        <v>76.72606659875018</v>
       </c>
       <c r="U6" t="n">
-        <v>76.72606659875015</v>
+        <v>76.72606659875018</v>
       </c>
       <c r="V6" t="n">
-        <v>6.333695197928724</v>
+        <v>6.333695197928717</v>
       </c>
       <c r="W6" t="n">
-        <v>6.339527032338275</v>
+        <v>6.339527032338268</v>
       </c>
       <c r="X6" t="n">
-        <v>6.332945429990315</v>
+        <v>6.332945429990318</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.429777836213171</v>
+        <v>6.429777836213166</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.332945429990315</v>
+        <v>6.332945429990318</v>
       </c>
       <c r="AA6" t="n">
-        <v>76.72606659875015</v>
+        <v>76.72606659875018</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.324912068780154</v>
+        <v>6.324912068780157</v>
       </c>
     </row>
     <row r="7">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4677928765408087</v>
+        <v>0.467792876540808</v>
       </c>
       <c r="C7" t="n">
         <v>0.4677928765408083</v>
@@ -5194,25 +5194,25 @@
         <v>0.4677928765408083</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4679766680039424</v>
+        <v>0.4679766680039429</v>
       </c>
       <c r="K7" t="n">
         <v>0.4677928765408083</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4677928765408089</v>
+        <v>0.467792876540808</v>
       </c>
       <c r="M7" t="n">
         <v>0.4677928765408083</v>
       </c>
       <c r="N7" t="n">
-        <v>2.110777612662492</v>
+        <v>0.4677928765408083</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4677676389116279</v>
+        <v>0.4677676389116288</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4677676389116279</v>
+        <v>0.4677676389116288</v>
       </c>
       <c r="Q7" t="n">
         <v>0.4677928765408083</v>
@@ -5227,16 +5227,16 @@
         <v>0.4677928765408083</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4679455536171568</v>
+        <v>0.4679455536171556</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4685426444792097</v>
+        <v>0.4685426444792076</v>
       </c>
       <c r="W7" t="n">
         <v>0.4677928765408083</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4677928765408089</v>
+        <v>0.467792876540808</v>
       </c>
       <c r="Y7" t="n">
         <v>0.4677928765408083</v>
@@ -5258,82 +5258,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5183006298406082</v>
+        <v>0.5183006298406072</v>
       </c>
       <c r="C8" t="n">
-        <v>0.798110625723878</v>
+        <v>0.7981106257238765</v>
       </c>
       <c r="D8" t="n">
-        <v>0.798110625723878</v>
+        <v>0.7981106257238765</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6491200568038989</v>
+        <v>0.6491200568038983</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5618917569866452</v>
+        <v>0.5618917569866441</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8561310511597164</v>
+        <v>0.8561310511597149</v>
       </c>
       <c r="H8" t="n">
-        <v>0.798110625723878</v>
+        <v>0.7981106257238765</v>
       </c>
       <c r="I8" t="n">
-        <v>0.798110625723878</v>
+        <v>0.7981106257238765</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7982944171870116</v>
+        <v>0.7982944171870111</v>
       </c>
       <c r="K8" t="n">
-        <v>0.798110625723878</v>
+        <v>0.7981106257238765</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7981106257238781</v>
+        <v>0.7981106257238759</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7981106257238223</v>
+        <v>0.7981106257238217</v>
       </c>
       <c r="N8" t="n">
-        <v>2.110777612662492</v>
+        <v>0.5812110677117092</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6408169495396228</v>
+        <v>0.6408169495396209</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6262061076258789</v>
+        <v>0.6262061076258797</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4633115793102622</v>
+        <v>0.4633115793102645</v>
       </c>
       <c r="R8" t="n">
-        <v>0.798110625723878</v>
+        <v>0.7981106257238765</v>
       </c>
       <c r="S8" t="n">
-        <v>0.798110625723878</v>
+        <v>0.7981106257238765</v>
       </c>
       <c r="T8" t="n">
-        <v>0.798110625723878</v>
+        <v>0.7981106257238765</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6616769808203663</v>
+        <v>0.6616769808203653</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7225361798248824</v>
+        <v>0.7225361798248795</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7981656163645173</v>
+        <v>0.7981656163645153</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4889567213984594</v>
+        <v>0.488956721398459</v>
       </c>
       <c r="Y8" t="n">
         <v>1.076555207489851</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5131030155167416</v>
+        <v>0.5131030155167424</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.798110625723878</v>
+        <v>0.7981106257238765</v>
       </c>
       <c r="AB8" t="n">
         <v>1.090395563715469</v>
@@ -5349,10 +5349,10 @@
         <v>2.25272195040112</v>
       </c>
       <c r="C9" t="n">
-        <v>2.854173312198541</v>
+        <v>2.854173312198546</v>
       </c>
       <c r="D9" t="n">
-        <v>2.854173312198541</v>
+        <v>2.854173312198546</v>
       </c>
       <c r="E9" t="n">
         <v>2.715360757050377</v>
@@ -5361,70 +5361,70 @@
         <v>1.467663829504012</v>
       </c>
       <c r="G9" t="n">
-        <v>2.854173267840149</v>
+        <v>2.854173267840147</v>
       </c>
       <c r="H9" t="n">
-        <v>2.854173312198541</v>
+        <v>2.854173312198546</v>
       </c>
       <c r="I9" t="n">
-        <v>2.854173312198541</v>
+        <v>2.854173312198546</v>
       </c>
       <c r="J9" t="n">
         <v>2.854357103661681</v>
       </c>
       <c r="K9" t="n">
-        <v>2.854173312198541</v>
+        <v>2.854173312198546</v>
       </c>
       <c r="L9" t="n">
-        <v>2.854173312198542</v>
+        <v>2.854173312198546</v>
       </c>
       <c r="M9" t="n">
-        <v>2.854173312198541</v>
+        <v>2.854173312198546</v>
       </c>
       <c r="N9" t="n">
-        <v>2.110777612662492</v>
+        <v>2.854173312198546</v>
       </c>
       <c r="O9" t="n">
-        <v>3.05349344690707</v>
+        <v>3.053493446907065</v>
       </c>
       <c r="P9" t="n">
-        <v>3.096842166094326</v>
+        <v>3.096842166094322</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.854173267840149</v>
+        <v>2.854173267840147</v>
       </c>
       <c r="R9" t="n">
-        <v>2.854173312198541</v>
+        <v>2.854173312198546</v>
       </c>
       <c r="S9" t="n">
-        <v>2.854173312198541</v>
+        <v>2.854173312198546</v>
       </c>
       <c r="T9" t="n">
-        <v>2.854173312198541</v>
+        <v>2.854173312198546</v>
       </c>
       <c r="U9" t="n">
-        <v>2.854173312198541</v>
+        <v>2.854173312198546</v>
       </c>
       <c r="V9" t="n">
-        <v>3.548984548666252</v>
+        <v>3.548984548666245</v>
       </c>
       <c r="W9" t="n">
-        <v>2.854173312198541</v>
+        <v>2.854173312198546</v>
       </c>
       <c r="X9" t="n">
-        <v>2.854173312198542</v>
+        <v>2.854173312198546</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.854173312198541</v>
+        <v>2.854173312198546</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.491551606562563</v>
+        <v>2.49155160656256</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.854173312198541</v>
+        <v>2.854173312198546</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.854173312198541</v>
+        <v>2.854173312198546</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1417092429723171</v>
+        <v>0.1417092429723178</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.7251214932466702</v>
+        <v>-0.72512149324667</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1748921610150536</v>
+        <v>-0.174892161015051</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5192474353127624</v>
+        <v>-0.5192474353127622</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7692433757105277</v>
+        <v>-0.7692433757105268</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08681516230203365</v>
+        <v>0.08681516230203627</v>
       </c>
       <c r="H10" t="n">
-        <v>0.05282716963273083</v>
+        <v>0.05282716963273067</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01559710090737623</v>
+        <v>-0.01559710090737599</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.00267258855222819</v>
+        <v>-0.002672588552226744</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.01093834492375873</v>
+        <v>-0.01093834492375809</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1074207523376054</v>
+        <v>-0.1074207523376052</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.03555911213478409</v>
+        <v>-0.03555911213478249</v>
       </c>
       <c r="N10" t="n">
         <v>0.1484137131639109</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06358709083120748</v>
+        <v>0.0635870908312075</v>
       </c>
       <c r="P10" t="n">
-        <v>0.04215448650772688</v>
+        <v>0.04215448650772727</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1308054721105032</v>
+        <v>0.1308054721105034</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.1494640829510595</v>
+        <v>-0.1494640829510591</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.06834146467044916</v>
+        <v>-0.06834146467044877</v>
       </c>
       <c r="T10" t="n">
-        <v>0.08383499886820675</v>
+        <v>0.08383499886820653</v>
       </c>
       <c r="U10" t="n">
-        <v>0.06301480632821178</v>
+        <v>0.06301480632821116</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0246485916352716</v>
+        <v>0.02464859163527282</v>
       </c>
       <c r="W10" t="n">
-        <v>0.06683514542374293</v>
+        <v>0.06683514542374336</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.105706112453808</v>
+        <v>-0.1057061124538084</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.09964199823656023</v>
+        <v>0.09964199823656109</v>
       </c>
       <c r="Z10" t="n">
         <v>0.1152314711792711</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.0348714391992055</v>
+        <v>-0.03487143919920532</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.08620030644610217</v>
+        <v>0.08620030644610256</v>
       </c>
     </row>
     <row r="11">
@@ -5522,85 +5522,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1766038845941843</v>
+        <v>0.1766038845941844</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0698682356565017</v>
+        <v>-0.06986823565650199</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08673403957323257</v>
+        <v>0.08673403957323361</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.03585963011654723</v>
+        <v>-0.0358596301165468</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.08142437130320913</v>
+        <v>-0.08142437130320888</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1608639961866042</v>
+        <v>0.1608639961866047</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1516330372872945</v>
+        <v>0.1516330372872947</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1320856257891546</v>
+        <v>0.1320856257891544</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1357403091290248</v>
+        <v>0.1357403091290253</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1332940373852811</v>
+        <v>0.1332940373852814</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1054440921483973</v>
+        <v>0.1054440921483969</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1264925734716258</v>
+        <v>0.1264925734716262</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1786123826598738</v>
+        <v>0.178612382659874</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1541660191357729</v>
+        <v>0.1541660191357727</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1479903592319558</v>
+        <v>0.147990359231956</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1736116043152321</v>
+        <v>0.1736116043152323</v>
       </c>
       <c r="R11" t="n">
-        <v>0.09419398649554843</v>
+        <v>0.09419398649554889</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1164736591579335</v>
+        <v>0.1164736591579345</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1602975476725791</v>
+        <v>0.1602975476725789</v>
       </c>
       <c r="U11" t="n">
-        <v>0.154141378567123</v>
+        <v>0.1541413785671231</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1707503854462981</v>
+        <v>0.1707503854462988</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1552909530682405</v>
+        <v>0.1552909530682398</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1063534485063148</v>
+        <v>0.1063534485063156</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1646850968709254</v>
+        <v>0.1646850968709258</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.1690215481697801</v>
+        <v>0.1690215481697803</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.126278154819391</v>
+        <v>0.1262781548193908</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.1609622881336741</v>
+        <v>0.1609622881336743</v>
       </c>
     </row>
   </sheetData>
@@ -6066,7 +6066,7 @@
         <v>0.1368752117279474</v>
       </c>
       <c r="N5" t="n">
-        <v>3.054452608428309</v>
+        <v>0.136875211727948</v>
       </c>
       <c r="O5" t="n">
         <v>0.136875211727948</v>
@@ -6154,7 +6154,7 @@
         <v>82.38097106811269</v>
       </c>
       <c r="N6" t="n">
-        <v>3.054452608428309</v>
+        <v>6.81571822606345</v>
       </c>
       <c r="O6" t="n">
         <v>82.37416188933038</v>
@@ -6242,7 +6242,7 @@
         <v>0.5169332128324172</v>
       </c>
       <c r="N7" t="n">
-        <v>3.054452608428309</v>
+        <v>0.5169332128324172</v>
       </c>
       <c r="O7" t="n">
         <v>0.5169060607053567</v>
@@ -6330,7 +6330,7 @@
         <v>0.8962819278105241</v>
       </c>
       <c r="N8" t="n">
-        <v>3.054452608428309</v>
+        <v>0.6530336447826105</v>
       </c>
       <c r="O8" t="n">
         <v>0.7198803850252957</v>
@@ -6418,7 +6418,7 @@
         <v>3.800045570772967</v>
       </c>
       <c r="N9" t="n">
-        <v>3.054452608428309</v>
+        <v>3.800045570772967</v>
       </c>
       <c r="O9" t="n">
         <v>4.066507172068674</v>
@@ -6829,7 +6829,7 @@
         <v>0.2255194596601565</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2249993937734921</v>
+        <v>0.224999393773492</v>
       </c>
       <c r="L2" t="n">
         <v>0.2298575683651301</v>
@@ -6874,7 +6874,7 @@
         <v>0.2061152847881987</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1994246400354058</v>
+        <v>0.1994246400354059</v>
       </c>
       <c r="AA2" t="n">
         <v>0.2226560017923063</v>
@@ -7102,7 +7102,7 @@
         <v>0.12200166101494</v>
       </c>
       <c r="N5" t="n">
-        <v>2.708985808850326</v>
+        <v>0.1220016610149396</v>
       </c>
       <c r="O5" t="n">
         <v>0.1220016610149398</v>
@@ -7190,7 +7190,7 @@
         <v>76.72489750080838</v>
       </c>
       <c r="N6" t="n">
-        <v>2.708985808850326</v>
+        <v>6.330054795984436</v>
       </c>
       <c r="O6" t="n">
         <v>76.71931127663551</v>
@@ -7242,61 +7242,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="J7" t="n">
         <v>0.4655530874514482</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="N7" t="n">
-        <v>2.708985808850326</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4652834804832711</v>
+        <v>0.4652834804832712</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4652834804832711</v>
+        <v>0.4652834804832712</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="U7" t="n">
         <v>0.4654068573989522</v>
@@ -7305,22 +7305,22 @@
         <v>0.4664468434034543</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.4653086761939625</v>
+        <v>0.4653086761939626</v>
       </c>
     </row>
     <row r="8">
@@ -7342,7 +7342,7 @@
         <v>0.6453014300394685</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5588659718473243</v>
+        <v>0.5588659718473244</v>
       </c>
       <c r="G8" t="n">
         <v>0.8504308454421304</v>
@@ -7366,7 +7366,7 @@
         <v>0.7929377833557588</v>
       </c>
       <c r="N8" t="n">
-        <v>2.708985808850326</v>
+        <v>0.5780096841287382</v>
       </c>
       <c r="O8" t="n">
         <v>0.6370737919654381</v>
@@ -7454,7 +7454,7 @@
         <v>3.105323695045696</v>
       </c>
       <c r="N9" t="n">
-        <v>2.708985808850326</v>
+        <v>3.105323695045696</v>
       </c>
       <c r="O9" t="n">
         <v>3.32257642496531</v>
@@ -7597,7 +7597,7 @@
         <v>0.1845363687545104</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.08721319020415516</v>
+        <v>-0.08721319020415515</v>
       </c>
       <c r="D11" t="n">
         <v>0.1212504715968136</v>
@@ -8138,7 +8138,7 @@
         <v>0.1096407592588043</v>
       </c>
       <c r="N5" t="n">
-        <v>1.89669139297879</v>
+        <v>0.1096407592588049</v>
       </c>
       <c r="O5" t="n">
         <v>0.1096407592588049</v>
@@ -8226,7 +8226,7 @@
         <v>76.68555410531536</v>
       </c>
       <c r="N6" t="n">
-        <v>1.89669139297879</v>
+        <v>6.304645011104051</v>
       </c>
       <c r="O6" t="n">
         <v>6.304643665765529</v>
@@ -8314,7 +8314,7 @@
         <v>0.4447464362450003</v>
       </c>
       <c r="N7" t="n">
-        <v>1.89669139297879</v>
+        <v>0.4447464362450003</v>
       </c>
       <c r="O7" t="n">
         <v>0.4447215293216525</v>
@@ -8402,7 +8402,7 @@
         <v>0.7532382498826515</v>
       </c>
       <c r="N8" t="n">
-        <v>1.89669139297879</v>
+        <v>0.5471020329879891</v>
       </c>
       <c r="O8" t="n">
         <v>0.6037500552232868</v>
@@ -8490,7 +8490,7 @@
         <v>2.763320625620714</v>
       </c>
       <c r="N9" t="n">
-        <v>1.89669139297879</v>
+        <v>2.763320625620714</v>
       </c>
       <c r="O9" t="n">
         <v>2.956773700996646</v>
@@ -9086,7 +9086,7 @@
         <v>11.60018423252597</v>
       </c>
       <c r="N4" t="n">
-        <v>2.631318073533905</v>
+        <v>2.631318073533907</v>
       </c>
       <c r="O4" t="n">
         <v>5.526544948989347</v>
@@ -9174,7 +9174,7 @@
         <v>0.1375231143614589</v>
       </c>
       <c r="N5" t="n">
-        <v>2.631318073533907</v>
+        <v>0.1375231143614593</v>
       </c>
       <c r="O5" t="n">
         <v>0.1375231143614593</v>
@@ -9262,7 +9262,7 @@
         <v>6.829268590655035</v>
       </c>
       <c r="N6" t="n">
-        <v>2.631318073533905</v>
+        <v>6.817032373954452</v>
       </c>
       <c r="O6" t="n">
         <v>82.37661956022367</v>
@@ -9350,7 +9350,7 @@
         <v>0.5161057285437461</v>
       </c>
       <c r="N7" t="n">
-        <v>2.631318073533905</v>
+        <v>0.5161057285437461</v>
       </c>
       <c r="O7" t="n">
         <v>0.516078556587834</v>
@@ -9438,7 +9438,7 @@
         <v>0.8898062561700265</v>
       </c>
       <c r="N8" t="n">
-        <v>2.631318073533905</v>
+        <v>0.6485149932854065</v>
       </c>
       <c r="O8" t="n">
         <v>0.7148239274012852</v>
@@ -9526,7 +9526,7 @@
         <v>3.839103635612084</v>
       </c>
       <c r="N9" t="n">
-        <v>2.631318073533905</v>
+        <v>3.839103635612084</v>
       </c>
       <c r="O9" t="n">
         <v>4.108368038626829</v>
@@ -10210,7 +10210,7 @@
         <v>0.1259318158198924</v>
       </c>
       <c r="N5" t="n">
-        <v>2.193254771195469</v>
+        <v>0.1259318158198923</v>
       </c>
       <c r="O5" t="n">
         <v>0.1259318158198923</v>
@@ -10298,7 +10298,7 @@
         <v>6.346177925302781</v>
       </c>
       <c r="N6" t="n">
-        <v>2.193254771195469</v>
+        <v>6.337753398936472</v>
       </c>
       <c r="O6" t="n">
         <v>76.73583064149868</v>
@@ -10386,7 +10386,7 @@
         <v>0.4755680360170785</v>
       </c>
       <c r="N7" t="n">
-        <v>2.193254771195469</v>
+        <v>0.4755680360170785</v>
       </c>
       <c r="O7" t="n">
         <v>0.4755428073790909</v>
@@ -10474,7 +10474,7 @@
         <v>0.8188776941638356</v>
       </c>
       <c r="N8" t="n">
-        <v>2.193254771195469</v>
+        <v>0.5966404867918345</v>
       </c>
       <c r="O8" t="n">
         <v>0.657713201009983</v>
@@ -10562,7 +10562,7 @@
         <v>3.157007680032965</v>
       </c>
       <c r="N9" t="n">
-        <v>2.193254771195469</v>
+        <v>3.157007680032965</v>
       </c>
       <c r="O9" t="n">
         <v>3.377851035783078</v>

--- a/Results/Phase 2/Hydrogen/hydrogen water use results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen water use results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.212649031550477</v>
+        <v>0.2126490315504762</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3940729698576902</v>
+        <v>0.3940729698576887</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4000495847228877</v>
+        <v>0.4000495847228871</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3751014818815375</v>
+        <v>0.3751014818815366</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3848922333811424</v>
+        <v>0.3848922333811418</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2220662161097739</v>
+        <v>0.2220662161097728</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2234666858663985</v>
+        <v>0.2234666858664001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2898389956868417</v>
+        <v>0.2898389956868412</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2393537183528854</v>
+        <v>0.239353718352885</v>
       </c>
       <c r="K2" t="n">
-        <v>0.243889786307466</v>
+        <v>0.2438897863074647</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2436336384984015</v>
+        <v>0.2436336384984039</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2417564755578361</v>
+        <v>0.2417564755578352</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2099624067692751</v>
+        <v>0.2099624067692747</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2179692335014831</v>
+        <v>0.2179692335014819</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2324718871075633</v>
+        <v>0.2324718871075628</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2088104925103795</v>
+        <v>0.2088104925103788</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2799913045949072</v>
+        <v>0.2799913045949062</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2513064501403381</v>
+        <v>0.2513064501403371</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2136861931246053</v>
+        <v>0.2136861931246038</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2519249928044283</v>
+        <v>0.2519249928044276</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2772946407420041</v>
+        <v>0.2772946407420033</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2313408773152023</v>
+        <v>0.2313408773152007</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2464917139259632</v>
+        <v>0.2464917139259609</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2216178989792534</v>
+        <v>0.221617898979252</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2195599641719674</v>
+        <v>0.2195599641719659</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2838780718495466</v>
+        <v>0.2838780718495453</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.215800998396598</v>
+        <v>0.2158009983965972</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1966798974274005</v>
+        <v>0.1966798974274004</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2013943066606985</v>
+        <v>0.2013943066606976</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2388113334391177</v>
+        <v>0.2388113334391174</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2013677175181817</v>
+        <v>0.2013677175181804</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.672090155134871</v>
+        <v>3.672090155134724</v>
       </c>
       <c r="C4" t="n">
-        <v>58.39000320475331</v>
+        <v>58.39000320475337</v>
       </c>
       <c r="D4" t="n">
-        <v>61.10400393633738</v>
+        <v>61.10400393633748</v>
       </c>
       <c r="E4" t="n">
-        <v>52.14138174488355</v>
+        <v>52.14138174488351</v>
       </c>
       <c r="F4" t="n">
-        <v>57.63883589036092</v>
+        <v>57.63883589036086</v>
       </c>
       <c r="G4" t="n">
-        <v>6.357568198221686</v>
+        <v>6.357568198221679</v>
       </c>
       <c r="H4" t="n">
-        <v>7.666933845194566</v>
+        <v>7.66693384519456</v>
       </c>
       <c r="I4" t="n">
-        <v>27.86778434722978</v>
+        <v>27.86778434722976</v>
       </c>
       <c r="J4" t="n">
-        <v>11.6020866854275</v>
+        <v>11.60208668542751</v>
       </c>
       <c r="K4" t="n">
-        <v>13.48851179110843</v>
+        <v>13.4885117911084</v>
       </c>
       <c r="L4" t="n">
-        <v>12.82868086344407</v>
+        <v>12.82868086344293</v>
       </c>
       <c r="M4" t="n">
-        <v>13.07823640231938</v>
+        <v>13.07823640231939</v>
       </c>
       <c r="N4" t="n">
-        <v>3.184022531470445</v>
+        <v>3.184022531470453</v>
       </c>
       <c r="O4" t="n">
-        <v>5.012550886670369</v>
+        <v>5.012550886670373</v>
       </c>
       <c r="P4" t="n">
-        <v>9.14746118571068</v>
+        <v>9.147461185710677</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.865294743813618</v>
+        <v>2.865294743813584</v>
       </c>
       <c r="R4" t="n">
-        <v>25.14103344830822</v>
+        <v>25.14103344830819</v>
       </c>
       <c r="S4" t="n">
-        <v>14.48100745232442</v>
+        <v>14.48100745232437</v>
       </c>
       <c r="T4" t="n">
-        <v>4.415147053629113</v>
+        <v>4.415147053629102</v>
       </c>
       <c r="U4" t="n">
-        <v>14.93913917974129</v>
+        <v>14.93913917974128</v>
       </c>
       <c r="V4" t="n">
-        <v>11.24060917300453</v>
+        <v>11.24060917300449</v>
       </c>
       <c r="W4" t="n">
-        <v>9.349406146143325</v>
+        <v>9.349406146143295</v>
       </c>
       <c r="X4" t="n">
-        <v>14.19299788310148</v>
+        <v>14.19299788310149</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.529993722802609</v>
+        <v>6.529993722802613</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.659667752369369</v>
+        <v>5.659667752369478</v>
       </c>
       <c r="AA4" t="n">
-        <v>24.79296065241245</v>
+        <v>24.79296065241243</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.296457782510688</v>
+        <v>5.29645778251068</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5987529466352582</v>
+        <v>0.5987529466352591</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9256652461990874</v>
+        <v>0.9256652461990813</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9256652461990874</v>
+        <v>0.9256652461990813</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7515940899993742</v>
+        <v>0.7515940899993767</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6496820621987177</v>
+        <v>0.649682062198717</v>
       </c>
       <c r="G5" t="n">
-        <v>0.993452641146175</v>
+        <v>0.993452641146173</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9256652461990874</v>
+        <v>0.9256652461990813</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9256652461990874</v>
+        <v>0.9256652461990813</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9257886922657719</v>
+        <v>0.9257886922657688</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9256652461990874</v>
+        <v>0.9256652461990813</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9256652461990874</v>
+        <v>0.9256652461990813</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9256652461990631</v>
+        <v>0.9256652461990579</v>
       </c>
       <c r="N5" t="n">
-        <v>3.184022531470445</v>
+        <v>0.6722535227914747</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7418932647010534</v>
+        <v>0.7418932647010523</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7248228812290246</v>
+        <v>0.7248228812290261</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5345072183735953</v>
+        <v>0.5345072183735917</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9256652461990874</v>
+        <v>0.9256652461990813</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9256652461990874</v>
+        <v>0.9256652461990813</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9256652461990874</v>
+        <v>0.9256652461990814</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7660758510572028</v>
+        <v>0.7660758510572009</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8366526758903089</v>
+        <v>0.8366526758903083</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9257294937944677</v>
+        <v>0.9257294937944642</v>
       </c>
       <c r="X5" t="n">
-        <v>0.564469380189112</v>
+        <v>0.5644693801891105</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.250659035813695</v>
+        <v>1.250659035813692</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5926803828381119</v>
+        <v>0.5926803828381131</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.9256652461990874</v>
+        <v>0.9256652461990813</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.267152479017682</v>
+        <v>1.26715247901768</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.63243062319589</v>
+        <v>3.632430623195885</v>
       </c>
       <c r="C6" t="n">
-        <v>4.613699270117315</v>
+        <v>4.613699270117313</v>
       </c>
       <c r="D6" t="n">
-        <v>4.613699270117315</v>
+        <v>4.613699270117313</v>
       </c>
       <c r="E6" t="n">
-        <v>4.387226512747106</v>
+        <v>4.387226512747096</v>
       </c>
       <c r="F6" t="n">
-        <v>2.351607150985547</v>
+        <v>2.351607150985544</v>
       </c>
       <c r="G6" t="n">
-        <v>4.613699327081957</v>
+        <v>4.61369932708195</v>
       </c>
       <c r="H6" t="n">
-        <v>4.613699270117315</v>
+        <v>4.613699270117313</v>
       </c>
       <c r="I6" t="n">
-        <v>4.613699270117315</v>
+        <v>4.613699270117313</v>
       </c>
       <c r="J6" t="n">
-        <v>4.613822716184004</v>
+        <v>4.613822716183998</v>
       </c>
       <c r="K6" t="n">
-        <v>4.613699270117315</v>
+        <v>4.613699270117313</v>
       </c>
       <c r="L6" t="n">
-        <v>4.613699270117315</v>
+        <v>4.613699270117313</v>
       </c>
       <c r="M6" t="n">
-        <v>4.613699270117315</v>
+        <v>4.613699270117313</v>
       </c>
       <c r="N6" t="n">
-        <v>3.184022531470445</v>
+        <v>4.613699270117313</v>
       </c>
       <c r="O6" t="n">
-        <v>4.938890490689075</v>
+        <v>4.938890490689066</v>
       </c>
       <c r="P6" t="n">
-        <v>5.009613989431257</v>
+        <v>5.009613989431252</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.613699327081957</v>
+        <v>4.61369932708195</v>
       </c>
       <c r="R6" t="n">
-        <v>4.613699270117315</v>
+        <v>4.613699270117313</v>
       </c>
       <c r="S6" t="n">
-        <v>4.613699270117315</v>
+        <v>4.613699270117313</v>
       </c>
       <c r="T6" t="n">
-        <v>4.613699270117315</v>
+        <v>4.613699270117313</v>
       </c>
       <c r="U6" t="n">
-        <v>4.613699270117315</v>
+        <v>4.613699270117313</v>
       </c>
       <c r="V6" t="n">
-        <v>5.746430026136387</v>
+        <v>5.746430026136385</v>
       </c>
       <c r="W6" t="n">
-        <v>4.613699270117315</v>
+        <v>4.613699270117313</v>
       </c>
       <c r="X6" t="n">
-        <v>4.613699270117315</v>
+        <v>4.613699270117313</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.613699270117315</v>
+        <v>4.613699270117313</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.022081556456614</v>
+        <v>4.02208155645661</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.613699270117315</v>
+        <v>4.613699270117313</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.613699270117315</v>
+        <v>4.613699270117313</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1251023953700026</v>
+        <v>0.1251023953700028</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.9377365066995207</v>
+        <v>-0.9377365066995218</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9714250257586736</v>
+        <v>-0.9714250257586734</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8669165247890667</v>
+        <v>-0.8669165247890659</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8773499309685452</v>
+        <v>-0.8773499309685459</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06915157006882756</v>
+        <v>0.06915157006882669</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0638496467148222</v>
+        <v>0.06384964671481974</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3248758034445594</v>
+        <v>-0.3248758034445614</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.03169898653301908</v>
+        <v>-0.03169898653302014</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.05708019599727204</v>
+        <v>-0.0570801959972729</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.05759402358349271</v>
+        <v>-0.05759402358348382</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.04328557640571246</v>
+        <v>-0.04328557640571351</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1417648540390134</v>
+        <v>0.1417648540390118</v>
       </c>
       <c r="O7" t="n">
-        <v>0.09333390232937122</v>
+        <v>0.09333390232937071</v>
       </c>
       <c r="P7" t="n">
-        <v>0.006788318349714981</v>
+        <v>0.006788318349713052</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1486290641830362</v>
+        <v>0.1486290641830358</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.2663290984895611</v>
+        <v>-0.2663290984895617</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1039312894062087</v>
+        <v>-0.1039312894062093</v>
       </c>
       <c r="T7" t="n">
         <v>0.1202560468369074</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1069187952883762</v>
+        <v>-0.1069187952883768</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.002349071371484435</v>
+        <v>-0.002349071371484328</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01538987978499303</v>
+        <v>0.0153898797849921</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.07221810129072637</v>
+        <v>-0.07221810129072413</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.07298256616797032</v>
+        <v>0.07298256616796897</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0841182680541764</v>
+        <v>0.08411826805417967</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.2942800426331013</v>
+        <v>-0.2942800426331015</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.107838207454431</v>
+        <v>0.1078382074544303</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1779480669298945</v>
+        <v>0.1779480669298929</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1242230822711378</v>
+        <v>-0.1242230822711389</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1335748509367938</v>
+        <v>-0.1335748509367959</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1088382797076416</v>
+        <v>-0.1088382797076433</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.105927734349493</v>
+        <v>-0.1059277343494947</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1619074476724564</v>
+        <v>0.1619074476724554</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1608955254067814</v>
+        <v>0.1608955254067808</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05039651661019878</v>
+        <v>0.05039651661019937</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1332955271254931</v>
+        <v>0.1332955271254908</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1262951620333029</v>
+        <v>0.1262951620333017</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1258052210350369</v>
+        <v>0.1258052210350366</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1304384471586768</v>
+        <v>0.1304384471586759</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1828429139431977</v>
+        <v>0.1828429139431964</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1688135033072334</v>
+        <v>0.1688135033072313</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1439376403981581</v>
+        <v>0.1439376403981582</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1848142371747717</v>
+        <v>0.1848142371747709</v>
       </c>
       <c r="R8" t="n">
-        <v>0.06718776285006789</v>
+        <v>0.06718776285006633</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1123944290595336</v>
+        <v>0.1123944290595334</v>
       </c>
       <c r="T8" t="n">
-        <v>0.176780124477068</v>
+        <v>0.1767801244770675</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1116536470266214</v>
+        <v>0.1116536470266193</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1675658880205702</v>
+        <v>0.1675658880205699</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1467203684703982</v>
+        <v>0.1467203684703973</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1220092945016368</v>
+        <v>0.1220092945016371</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1632022459757058</v>
+        <v>0.1632022459757044</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1662110910140204</v>
+        <v>0.166211091014018</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.05835676144502173</v>
+        <v>0.05835676144502049</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1732447732567277</v>
+        <v>0.1732447732567265</v>
       </c>
     </row>
   </sheetData>
@@ -1358,67 +1358,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1881243997788272</v>
+        <v>0.1881243997788274</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3454728904173844</v>
+        <v>0.3454728904173848</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2219509087104088</v>
+        <v>0.2219509087104085</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2703964878408673</v>
+        <v>0.270396487840867</v>
       </c>
       <c r="F2" t="n">
         <v>0.3811106490995785</v>
       </c>
       <c r="G2" t="n">
-        <v>0.197530395314138</v>
+        <v>0.1975303953141382</v>
       </c>
       <c r="H2" t="n">
-        <v>0.21379631500209</v>
+        <v>0.2137963150020898</v>
       </c>
       <c r="I2" t="n">
         <v>0.2189973382660556</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2195831060355364</v>
+        <v>0.2195831060355366</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2275004499214466</v>
+        <v>0.2275004499214469</v>
       </c>
       <c r="L2" t="n">
         <v>0.2439581687448542</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2363200048841411</v>
+        <v>0.2363200048841413</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1935166526280889</v>
+        <v>0.1935166526280888</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2087367784499916</v>
+        <v>0.2087367784499917</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2211089179827077</v>
+        <v>0.2211089179827078</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1898799054845603</v>
+        <v>0.1898799054845604</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2236140676113255</v>
+        <v>0.2236140676113252</v>
       </c>
       <c r="S2" t="n">
-        <v>0.239817888359914</v>
+        <v>0.2398178883599139</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2029731678948745</v>
+        <v>0.202973167894875</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2159086790503663</v>
+        <v>0.2159086790503662</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2507430872426785</v>
+        <v>0.2507430872426778</v>
       </c>
       <c r="W2" t="n">
         <v>0.2057084571343957</v>
@@ -1427,16 +1427,16 @@
         <v>0.2376150050080583</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1957398443777496</v>
+        <v>0.1957398443777495</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1931912167847061</v>
+        <v>0.1931912167847067</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2130070447063746</v>
+        <v>0.2130070447063745</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2043213019695516</v>
+        <v>0.2043213019695517</v>
       </c>
     </row>
     <row r="3">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1569587768180558</v>
+        <v>0.1569587768180555</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1875217126472719</v>
+        <v>0.1875217126472723</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2241549721041018</v>
+        <v>0.2241549721041009</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1873389371525004</v>
+        <v>0.1873389371525006</v>
       </c>
     </row>
     <row r="4">
@@ -1534,52 +1534,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7068167190142102</v>
+        <v>0.7068167190142087</v>
       </c>
       <c r="C4" t="n">
-        <v>38.98903486147651</v>
+        <v>38.98903486147653</v>
       </c>
       <c r="D4" t="n">
-        <v>9.146426742391421</v>
+        <v>9.146426742391434</v>
       </c>
       <c r="E4" t="n">
-        <v>26.6384626647758</v>
+        <v>26.63846266477577</v>
       </c>
       <c r="F4" t="n">
-        <v>49.83869606064724</v>
+        <v>49.83869606064722</v>
       </c>
       <c r="G4" t="n">
-        <v>2.828843932131576</v>
+        <v>2.828843932131568</v>
       </c>
       <c r="H4" t="n">
-        <v>7.681550598687148</v>
+        <v>7.68155059868715</v>
       </c>
       <c r="I4" t="n">
         <v>8.751968129198554</v>
       </c>
       <c r="J4" t="n">
-        <v>8.293684055026818</v>
+        <v>8.293684055026814</v>
       </c>
       <c r="K4" t="n">
-        <v>9.737220166342206</v>
+        <v>9.737220166342205</v>
       </c>
       <c r="L4" t="n">
-        <v>13.42634538441377</v>
+        <v>13.42634538441379</v>
       </c>
       <c r="M4" t="n">
-        <v>12.87818795563308</v>
+        <v>12.87818795563307</v>
       </c>
       <c r="N4" t="n">
-        <v>2.122822966128353</v>
+        <v>2.122822966128355</v>
       </c>
       <c r="O4" t="n">
-        <v>5.301687549043066</v>
+        <v>5.301687549043072</v>
       </c>
       <c r="P4" t="n">
-        <v>8.137024693236755</v>
+        <v>8.137024693236754</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.163515760499158</v>
+        <v>1.163515760499156</v>
       </c>
       <c r="R4" t="n">
         <v>10.24054667475356</v>
@@ -1588,28 +1588,28 @@
         <v>12.35324105572277</v>
       </c>
       <c r="T4" t="n">
-        <v>4.644576777536453</v>
+        <v>4.644576777536454</v>
       </c>
       <c r="U4" t="n">
-        <v>6.937392285311301</v>
+        <v>6.937392285311267</v>
       </c>
       <c r="V4" t="n">
-        <v>6.652498703573016</v>
+        <v>6.652498703573023</v>
       </c>
       <c r="W4" t="n">
-        <v>5.143587946612469</v>
+        <v>5.143587946612468</v>
       </c>
       <c r="X4" t="n">
-        <v>12.82084653482583</v>
+        <v>12.82084653482585</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.67272845865721</v>
+        <v>2.672728458657216</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.812659680969723</v>
+        <v>1.812659680969725</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.070198748689688</v>
+        <v>7.070198748689691</v>
       </c>
       <c r="AB4" t="n">
         <v>5.166720200936132</v>
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5072189007010943</v>
+        <v>0.5072189007010944</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7839740862891132</v>
+        <v>0.7839740862891117</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7839740862891132</v>
+        <v>0.7839740862891117</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6366101137396224</v>
+        <v>0.6366101137396221</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5503341241058392</v>
+        <v>0.5503341241058375</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8413610769101065</v>
+        <v>0.8413610769101052</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7839740862891132</v>
+        <v>0.7839740862891117</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7839740862891132</v>
+        <v>0.7839740862891117</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7841344843981575</v>
+        <v>0.784134484398156</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7839740862891132</v>
+        <v>0.7839740862891117</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7839740862891132</v>
+        <v>0.7839740862891117</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7839740862891333</v>
+        <v>0.783974086289131</v>
       </c>
       <c r="N5" t="n">
-        <v>2.122822966128353</v>
+        <v>0.5694425173149745</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6283976551954547</v>
+        <v>0.6283976551954538</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6139463263473091</v>
+        <v>0.6139463263473081</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4528301901158462</v>
+        <v>0.4528301901158467</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7839740862891132</v>
+        <v>0.7839740862891117</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7839740862891132</v>
+        <v>0.7839740862891117</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7839740862891132</v>
+        <v>0.7839740862891117</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6489333189608202</v>
+        <v>0.6489333189608187</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7089776011031808</v>
+        <v>0.7089776011031792</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7840284765741575</v>
+        <v>0.7840284765741548</v>
       </c>
       <c r="X5" t="n">
-        <v>0.478195352771824</v>
+        <v>0.4781953527718228</v>
       </c>
       <c r="Y5" t="n">
         <v>1.059213460032236</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5020780310466501</v>
+        <v>0.5020780310466505</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.7839740862891132</v>
+        <v>0.7839740862891117</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.07306801949024</v>
+        <v>1.073068019490238</v>
       </c>
     </row>
     <row r="6">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.219975591961776</v>
+        <v>2.219975591961778</v>
       </c>
       <c r="C6" t="n">
-        <v>2.81410594171921</v>
+        <v>2.814105941719208</v>
       </c>
       <c r="D6" t="n">
-        <v>2.81410594171921</v>
+        <v>2.814105941719208</v>
       </c>
       <c r="E6" t="n">
-        <v>2.676982993808483</v>
+        <v>2.676982993808484</v>
       </c>
       <c r="F6" t="n">
-        <v>1.444473478923864</v>
+        <v>1.444473478923865</v>
       </c>
       <c r="G6" t="n">
-        <v>2.81410582913504</v>
+        <v>2.814105829135039</v>
       </c>
       <c r="H6" t="n">
-        <v>2.81410594171921</v>
+        <v>2.814105941719208</v>
       </c>
       <c r="I6" t="n">
-        <v>2.81410594171921</v>
+        <v>2.814105941719208</v>
       </c>
       <c r="J6" t="n">
-        <v>2.814266339828252</v>
+        <v>2.814266339828249</v>
       </c>
       <c r="K6" t="n">
-        <v>2.81410594171921</v>
+        <v>2.814105941719208</v>
       </c>
       <c r="L6" t="n">
-        <v>2.81410594171921</v>
+        <v>2.814105941719208</v>
       </c>
       <c r="M6" t="n">
-        <v>2.81410594171921</v>
+        <v>2.814105941719208</v>
       </c>
       <c r="N6" t="n">
-        <v>2.122822966128353</v>
+        <v>2.814105941719208</v>
       </c>
       <c r="O6" t="n">
-        <v>3.010999811788023</v>
+        <v>3.010999811788021</v>
       </c>
       <c r="P6" t="n">
-        <v>3.053820874881778</v>
+        <v>3.05382087488178</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.81410582913504</v>
+        <v>2.814105829135039</v>
       </c>
       <c r="R6" t="n">
-        <v>2.81410594171921</v>
+        <v>2.814105941719208</v>
       </c>
       <c r="S6" t="n">
-        <v>2.81410594171921</v>
+        <v>2.814105941719208</v>
       </c>
       <c r="T6" t="n">
-        <v>2.81410594171921</v>
+        <v>2.814105941719208</v>
       </c>
       <c r="U6" t="n">
-        <v>2.81410594171921</v>
+        <v>2.814105941719208</v>
       </c>
       <c r="V6" t="n">
-        <v>3.5003200197022</v>
+        <v>3.500320019702199</v>
       </c>
       <c r="W6" t="n">
-        <v>2.81410594171921</v>
+        <v>2.814105941719208</v>
       </c>
       <c r="X6" t="n">
-        <v>2.81410594171921</v>
+        <v>2.814105941719208</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.81410594171921</v>
+        <v>2.814105941719208</v>
       </c>
       <c r="Z6" t="n">
         <v>2.455898128241858</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.81410594171921</v>
+        <v>2.814105941719208</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.81410594171921</v>
+        <v>2.814105941719208</v>
       </c>
     </row>
     <row r="7">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1741811903940636</v>
+        <v>0.1741811903940634</v>
       </c>
       <c r="C7" t="n">
         <v>-0.7483716180783239</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.02375364388579725</v>
+        <v>-0.02375364388579734</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5194874362813058</v>
+        <v>-0.5194874362813053</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.950456739109121</v>
+        <v>-0.9504567391091208</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1182618082734633</v>
+        <v>0.118261808273463</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02511461927554822</v>
+        <v>0.02511461927554793</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.006089967610861953</v>
+        <v>-0.006089967610861887</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.009377260565933805</v>
+        <v>-0.00937726056593409</v>
       </c>
       <c r="K7" t="n">
         <v>-0.05660582334644701</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1558155486991682</v>
+        <v>-0.1558155486991684</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1068000149126745</v>
+        <v>-0.1068000149126741</v>
       </c>
       <c r="N7" t="n">
-        <v>0.142611850079532</v>
+        <v>0.1426118500795316</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05140654879219608</v>
+        <v>0.05140654879219614</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.02246394298080062</v>
+        <v>-0.02246394298080054</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1640434615291627</v>
+        <v>0.1640434615291622</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.03262490163947454</v>
+        <v>-0.0326249016394745</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1323617519277663</v>
+        <v>-0.1323617519277668</v>
       </c>
       <c r="T7" t="n">
-        <v>0.08747261778954496</v>
+        <v>0.08747261778954477</v>
       </c>
       <c r="U7" t="n">
-        <v>0.009831337283997273</v>
+        <v>0.0098313372839978</v>
       </c>
       <c r="V7" t="n">
-        <v>0.05441128020948928</v>
+        <v>0.05441128020948836</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07050609568301382</v>
+        <v>0.07050609568301397</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1157981200793693</v>
+        <v>-0.1157981200793684</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1294345013460685</v>
+        <v>0.1294345013460682</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.144085959334973</v>
+        <v>0.1440859593349734</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02756011682938786</v>
+        <v>0.02756011682938777</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.07953693301908893</v>
+        <v>0.07953693301908903</v>
       </c>
     </row>
     <row r="8">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1821375830724869</v>
+        <v>0.1821375830724863</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.08027839414524984</v>
+        <v>-0.0802783941452497</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1259031116258416</v>
+        <v>0.1259031116258411</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0373886948255165</v>
+        <v>-0.03738869482551713</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1365900095391381</v>
+        <v>-0.1365900095391389</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1661000815384279</v>
+        <v>0.1661000815384273</v>
       </c>
       <c r="H8" t="n">
         <v>0.1399837333898498</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1309865701773807</v>
+        <v>0.1309865701773806</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1299934457437306</v>
+        <v>0.1299934457437308</v>
       </c>
       <c r="K8" t="n">
         <v>0.1165048064886006</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08782178411388455</v>
+        <v>0.08782178411388429</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1024858443292636</v>
+        <v>0.1024858443292635</v>
       </c>
       <c r="N8" t="n">
         <v>0.1731656854731181</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1468871085552345</v>
+        <v>0.1468871085552349</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1256479389199471</v>
+        <v>0.1256479389199469</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1792803898376668</v>
+        <v>0.1792803898376667</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1235298199778146</v>
+        <v>0.1235298199778143</v>
       </c>
       <c r="S8" t="n">
-        <v>0.09435305600274771</v>
+        <v>0.09435305600274742</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1575336743296534</v>
+        <v>0.1575336743296535</v>
       </c>
       <c r="U8" t="n">
         <v>0.1351421554270403</v>
       </c>
       <c r="V8" t="n">
-        <v>0.173509166489579</v>
+        <v>0.1735091664895786</v>
       </c>
       <c r="W8" t="n">
         <v>0.1525491419416045</v>
       </c>
       <c r="X8" t="n">
-        <v>0.09968667792707561</v>
+        <v>0.09968667792707557</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1693931415553342</v>
+        <v>0.1693931415553344</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1735109740386695</v>
+        <v>0.1735109740386699</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.14030717227447</v>
+        <v>0.1403071722744695</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1552710465442456</v>
+        <v>0.1552710465442458</v>
       </c>
     </row>
   </sheetData>
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2116686499472774</v>
+        <v>0.2116686499472779</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3896022628288887</v>
+        <v>0.389602262828889</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3262302459386223</v>
+        <v>0.3262302459386226</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3650459383050797</v>
+        <v>0.3650459383050808</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4006448818623256</v>
+        <v>0.4006448818623263</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2221895808827974</v>
+        <v>0.2221895808827978</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2323962819385783</v>
+        <v>0.2323962819385784</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3064591005680445</v>
+        <v>0.3064591005680447</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2414331886812571</v>
+        <v>0.2414331886812574</v>
       </c>
       <c r="K2" t="n">
         <v>0.2526318305535128</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2552821758320904</v>
+        <v>0.2552821758320919</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2430754072229455</v>
+        <v>0.2430754072229457</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2108810932612018</v>
+        <v>0.2108810932612024</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2234535121623897</v>
+        <v>0.22345351216239</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2335522464434844</v>
+        <v>0.233552246443485</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2100991843368161</v>
+        <v>0.2100991843368168</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2779745579149162</v>
+        <v>0.2779745579149164</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2646467289861738</v>
+        <v>0.2646467289861739</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2144335094150676</v>
+        <v>0.2144335094150679</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2485114720617253</v>
+        <v>0.2485114720617257</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2842841444880834</v>
+        <v>0.2842841444880837</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2280177801109134</v>
+        <v>0.2280177801109137</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2493820482790911</v>
+        <v>0.2493820482790917</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.222611382767152</v>
+        <v>0.2226113827671521</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2200355835057884</v>
+        <v>0.2200355835057893</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2698206689535083</v>
+        <v>0.2698206689535086</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2166698749104516</v>
+        <v>0.2166698749104518</v>
       </c>
     </row>
     <row r="3">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1934805816569787</v>
+        <v>0.1934805816569793</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2029187629602398</v>
+        <v>0.2029187629602403</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2425141798612506</v>
+        <v>0.2425141798612509</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2026292324276749</v>
+        <v>0.2026292324276752</v>
       </c>
     </row>
     <row r="4">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.870362965003835</v>
+        <v>2.870362965003916</v>
       </c>
       <c r="C4" t="n">
-        <v>51.57557956883807</v>
+        <v>51.57557956883808</v>
       </c>
       <c r="D4" t="n">
-        <v>35.81258680703913</v>
+        <v>35.81258680703911</v>
       </c>
       <c r="E4" t="n">
-        <v>46.75918438440532</v>
+        <v>46.75918438440545</v>
       </c>
       <c r="F4" t="n">
-        <v>56.79360779183872</v>
+        <v>56.79360779183883</v>
       </c>
       <c r="G4" t="n">
-        <v>5.623724232026251</v>
+        <v>5.623724232026265</v>
       </c>
       <c r="H4" t="n">
-        <v>9.416765807453499</v>
+        <v>9.416765807453507</v>
       </c>
       <c r="I4" t="n">
         <v>30.50924195241406</v>
       </c>
       <c r="J4" t="n">
-        <v>10.93129310306286</v>
+        <v>10.93129310306281</v>
       </c>
       <c r="K4" t="n">
         <v>13.79127003210087</v>
       </c>
       <c r="L4" t="n">
-        <v>14.82278015321573</v>
+        <v>14.82278015321588</v>
       </c>
       <c r="M4" t="n">
-        <v>12.20409908922312</v>
+        <v>12.20409908922302</v>
       </c>
       <c r="N4" t="n">
         <v>2.895763566501031</v>
       </c>
       <c r="O4" t="n">
-        <v>5.688173203260279</v>
+        <v>5.688173203260282</v>
       </c>
       <c r="P4" t="n">
-        <v>8.503719203019799</v>
+        <v>8.5037192030199</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.690931193637341</v>
+        <v>2.690931193637389</v>
       </c>
       <c r="R4" t="n">
-        <v>22.58257396372515</v>
+        <v>22.58257396372514</v>
       </c>
       <c r="S4" t="n">
-        <v>16.53149165776676</v>
+        <v>16.53149165776675</v>
       </c>
       <c r="T4" t="n">
-        <v>3.982811167690388</v>
+        <v>3.982811167690426</v>
       </c>
       <c r="U4" t="n">
-        <v>12.72437910379082</v>
+        <v>12.72437910379081</v>
       </c>
       <c r="V4" t="n">
         <v>10.96791341710475</v>
       </c>
       <c r="W4" t="n">
-        <v>7.513118075641283</v>
+        <v>7.513118075641284</v>
       </c>
       <c r="X4" t="n">
-        <v>13.6819118050368</v>
+        <v>13.68191180503687</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.996018387059521</v>
+        <v>5.996018387059522</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.071155764655853</v>
+        <v>5.071155764655842</v>
       </c>
       <c r="AA4" t="n">
-        <v>18.85233767378783</v>
+        <v>18.85233767378788</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.853398087642428</v>
+        <v>4.853398087642558</v>
       </c>
     </row>
     <row r="5">
@@ -2397,82 +2397,82 @@
         <v>0.5723768781925502</v>
       </c>
       <c r="C5" t="n">
-        <v>0.880937518294743</v>
+        <v>0.8809375182947452</v>
       </c>
       <c r="D5" t="n">
-        <v>0.880937518294743</v>
+        <v>0.8809375182947452</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7166380794189812</v>
+        <v>0.7166380794189823</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6204470196920633</v>
+        <v>0.6204470196920637</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9449195771025836</v>
+        <v>0.9449195771025826</v>
       </c>
       <c r="H5" t="n">
-        <v>0.880937518294743</v>
+        <v>0.8809375182947452</v>
       </c>
       <c r="I5" t="n">
-        <v>0.880937518294743</v>
+        <v>0.8809375182947452</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8811128082132814</v>
+        <v>0.8811128082132796</v>
       </c>
       <c r="K5" t="n">
-        <v>0.880937518294743</v>
+        <v>0.8809375182947452</v>
       </c>
       <c r="L5" t="n">
-        <v>0.880937518294743</v>
+        <v>0.8809375182947452</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8809375182946469</v>
+        <v>0.8809375182946481</v>
       </c>
       <c r="N5" t="n">
-        <v>2.895763566501031</v>
+        <v>0.6417514011353108</v>
       </c>
       <c r="O5" t="n">
-        <v>0.707481822928494</v>
+        <v>0.7074818229284932</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6913697082795789</v>
+        <v>0.6913697082795809</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5117376698714948</v>
+        <v>0.5117376698714929</v>
       </c>
       <c r="R5" t="n">
-        <v>0.880937518294743</v>
+        <v>0.8809375182947435</v>
       </c>
       <c r="S5" t="n">
-        <v>0.880937518294743</v>
+        <v>0.8809375182947452</v>
       </c>
       <c r="T5" t="n">
-        <v>0.880937518294743</v>
+        <v>0.8809375182947435</v>
       </c>
       <c r="U5" t="n">
         <v>0.7303051636864679</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7972713468437836</v>
+        <v>0.7972713468437822</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8809981592620156</v>
+        <v>0.8809981592620142</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5400178656315111</v>
+        <v>0.5400178656315089</v>
       </c>
       <c r="Y5" t="n">
         <v>1.187684397738151</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5666452058916722</v>
+        <v>0.5666452058916732</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.880937518294743</v>
+        <v>0.8809375182947452</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.203254908263838</v>
+        <v>1.203254908263843</v>
       </c>
     </row>
     <row r="6">
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.010713164452654</v>
+        <v>3.010713164452651</v>
       </c>
       <c r="C6" t="n">
         <v>3.819349540753903</v>
@@ -2491,13 +2491,13 @@
         <v>3.819349540753903</v>
       </c>
       <c r="E6" t="n">
-        <v>3.63271957781865</v>
+        <v>3.632719577818649</v>
       </c>
       <c r="F6" t="n">
-        <v>1.955221971226523</v>
+        <v>1.955221971226521</v>
       </c>
       <c r="G6" t="n">
-        <v>3.819349559406224</v>
+        <v>3.819349559406227</v>
       </c>
       <c r="H6" t="n">
         <v>3.819349540753903</v>
@@ -2506,7 +2506,7 @@
         <v>3.819349540753903</v>
       </c>
       <c r="J6" t="n">
-        <v>3.819524830672445</v>
+        <v>3.819524830672441</v>
       </c>
       <c r="K6" t="n">
         <v>3.819349540753903</v>
@@ -2518,16 +2518,16 @@
         <v>3.819349540753903</v>
       </c>
       <c r="N6" t="n">
-        <v>2.895763566501031</v>
+        <v>3.819349540753903</v>
       </c>
       <c r="O6" t="n">
-        <v>4.087330601875786</v>
+        <v>4.08733060187579</v>
       </c>
       <c r="P6" t="n">
-        <v>4.145611880831026</v>
+        <v>4.145611880831024</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.819349559406224</v>
+        <v>3.819349559406227</v>
       </c>
       <c r="R6" t="n">
         <v>3.819349540753903</v>
@@ -2554,7 +2554,7 @@
         <v>3.819349540753903</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.331813720003314</v>
+        <v>3.331813720003311</v>
       </c>
       <c r="AA6" t="n">
         <v>3.819349540753903</v>
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1396178939744717</v>
+        <v>0.139617893974473</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.9029416335512851</v>
+        <v>-0.9029416335512842</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5304572019253192</v>
+        <v>-0.5304572019253179</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8292621728450126</v>
+        <v>-0.829262172845015</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.960638240392621</v>
+        <v>-0.9606382403926215</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07709697275202577</v>
+        <v>0.07709697275202632</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02041642750947115</v>
+        <v>0.02041642750947143</v>
       </c>
       <c r="I7" t="n">
         <v>-0.4134913112237402</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.03335268398027743</v>
+        <v>-0.03335268398027719</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.09978051303451139</v>
+        <v>-0.09978051303451109</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1178218348295748</v>
+        <v>-0.1178218348295629</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.04244094909908597</v>
+        <v>-0.04244094909908635</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1449604874047649</v>
+        <v>0.1449604874047654</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06936256989856462</v>
+        <v>0.0693625698985649</v>
       </c>
       <c r="P7" t="n">
-        <v>0.009046078132966248</v>
+        <v>0.009046078132966942</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1496486148869677</v>
+        <v>0.1496486148869678</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.2460225576556552</v>
+        <v>-0.2460225576556547</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1743897638605182</v>
+        <v>-0.1743897638605191</v>
       </c>
       <c r="T7" t="n">
         <v>0.1244454798790307</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07807463457124388</v>
+        <v>-0.07807463457124365</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.01840326741136824</v>
+        <v>-0.01840326741136812</v>
       </c>
       <c r="W7" t="n">
-        <v>0.04362687867717995</v>
+        <v>0.04362687867718029</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0805888631042574</v>
+        <v>-0.08058886310425636</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.07574079125612414</v>
+        <v>0.07574079125612482</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.08996667836735747</v>
+        <v>0.08996667836735793</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.2027628488046375</v>
+        <v>-0.2027628488046376</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1113169505821254</v>
+        <v>0.1113169505821242</v>
       </c>
     </row>
     <row r="8">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1829982901458488</v>
+        <v>0.1829982901458501</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1134360044368399</v>
+        <v>-0.1134360044368397</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.007326417899840146</v>
+        <v>-0.007326417899840264</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.100305274281097</v>
+        <v>-0.1003052742810969</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1286455253843879</v>
+        <v>-0.1286455253843871</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1650720026828021</v>
+        <v>0.1650720026828027</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1494888750230401</v>
+        <v>0.1494888750230404</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02612228974697762</v>
+        <v>0.02612228974697785</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1339289273708966</v>
+        <v>0.133928927370897</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1150344326455397</v>
+        <v>0.11503443264554</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1094759190130832</v>
+        <v>0.109475919013083</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1315676936359401</v>
+        <v>0.1315676936359403</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1846416304963913</v>
+        <v>0.1846416304963918</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1628167560159896</v>
+        <v>0.16281675601599</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1454712943264833</v>
+        <v>0.1454712943264837</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1859928345165837</v>
+        <v>0.1859928345165845</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0738365636585816</v>
+        <v>0.07383656365858171</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0931018841867942</v>
+        <v>0.09310188418679451</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1788596528485977</v>
+        <v>0.1788596528485976</v>
       </c>
       <c r="U8" t="n">
         <v>0.1207903180270703</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1655658744844733</v>
+        <v>0.1655658744844732</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1556712024440011</v>
+        <v>0.1556712024440012</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1205169122495441</v>
+        <v>0.1205169122495439</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.164876737664626</v>
+        <v>0.1648767376646263</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1687737623740867</v>
+        <v>0.1687737623740876</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0853659800848979</v>
+        <v>0.08536598008489832</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1751224956757499</v>
+        <v>0.1751224956757498</v>
       </c>
     </row>
   </sheetData>
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2057364986957491</v>
+        <v>0.2057364986957495</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3489674397838791</v>
+        <v>0.348967439783879</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2755397362205877</v>
+        <v>0.2755397362205886</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2920091013157562</v>
+        <v>0.2920091013157563</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3834546949446041</v>
+        <v>0.3834546949446044</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2162181520798261</v>
+        <v>0.2162181520798263</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2249935988273187</v>
+        <v>0.2249935988273189</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2498347327052109</v>
+        <v>0.2498347327052111</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2319384571857372</v>
+        <v>0.2319384571857373</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2392442443802597</v>
+        <v>0.23924424438026</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2477901009897552</v>
+        <v>0.2477901009897554</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2292941748927843</v>
+        <v>0.2292941748927842</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2050618839099853</v>
+        <v>0.2050618839099854</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2215378160743192</v>
+        <v>0.2215378160743195</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2272441929392685</v>
+        <v>0.2272441929392688</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2061383776796321</v>
+        <v>0.2061383776796324</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2716488035186409</v>
+        <v>0.271648803518641</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2458162705525948</v>
+        <v>0.2458162705525951</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2135342761836123</v>
+        <v>0.2135342761836125</v>
       </c>
       <c r="U2" t="n">
         <v>0.2278815164886976</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2774831629783526</v>
+        <v>0.2774831629783529</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2219281962897266</v>
+        <v>0.221928196289727</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2461191598344221</v>
+        <v>0.2461191598344228</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2161398800948544</v>
+        <v>0.2161398800948546</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2133630349185317</v>
+        <v>0.2133630349185319</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2448537700639762</v>
+        <v>0.2448537700639764</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2150228750868996</v>
+        <v>0.2150228750868998</v>
       </c>
     </row>
     <row r="3">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1668585234218753</v>
+        <v>0.1668585234218751</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="J3" t="n">
-        <v>0.198388809238074</v>
+        <v>0.1983888092380743</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2389131503051229</v>
+        <v>0.2389131503051228</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1980463244144165</v>
+        <v>0.1980463244144167</v>
       </c>
     </row>
     <row r="4">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.369067877068553</v>
+        <v>2.369067877068467</v>
       </c>
       <c r="C4" t="n">
         <v>37.60962010785784</v>
       </c>
       <c r="D4" t="n">
-        <v>20.91824698787185</v>
+        <v>20.91824698787184</v>
       </c>
       <c r="E4" t="n">
-        <v>31.9359202807604</v>
+        <v>31.93592028076034</v>
       </c>
       <c r="F4" t="n">
-        <v>48.79531580806316</v>
+        <v>48.79531580806317</v>
       </c>
       <c r="G4" t="n">
-        <v>4.835367328225798</v>
+        <v>4.835367328225807</v>
       </c>
       <c r="H4" t="n">
         <v>8.037336020978653</v>
       </c>
       <c r="I4" t="n">
-        <v>14.40213728324733</v>
+        <v>14.40213728324731</v>
       </c>
       <c r="J4" t="n">
         <v>8.866134396091748</v>
       </c>
       <c r="K4" t="n">
-        <v>10.21946146055984</v>
+        <v>10.21946146055981</v>
       </c>
       <c r="L4" t="n">
-        <v>13.00422565061847</v>
+        <v>13.0042256506185</v>
       </c>
       <c r="M4" t="n">
-        <v>8.924830176907962</v>
+        <v>8.92483017690796</v>
       </c>
       <c r="N4" t="n">
-        <v>2.371762749345276</v>
+        <v>2.371762749345288</v>
       </c>
       <c r="O4" t="n">
-        <v>5.835660041682074</v>
+        <v>5.835660041682082</v>
       </c>
       <c r="P4" t="n">
-        <v>7.41788608655995</v>
+        <v>7.417886086559962</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.617525759513475</v>
+        <v>2.617525759513474</v>
       </c>
       <c r="R4" t="n">
-        <v>20.55844571975663</v>
+        <v>20.55844571975664</v>
       </c>
       <c r="S4" t="n">
         <v>11.87843648749993</v>
       </c>
       <c r="T4" t="n">
-        <v>4.682681499992402</v>
+        <v>4.682681499992403</v>
       </c>
       <c r="U4" t="n">
-        <v>7.811678258578866</v>
+        <v>7.811678258578855</v>
       </c>
       <c r="V4" t="n">
-        <v>9.355646168771358</v>
+        <v>9.355646168771395</v>
       </c>
       <c r="W4" t="n">
-        <v>6.61029792026662</v>
+        <v>6.610297920266634</v>
       </c>
       <c r="X4" t="n">
-        <v>13.01752415599063</v>
+        <v>13.01752415599073</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.112889507983077</v>
+        <v>5.112889507983107</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.006361642765637</v>
+        <v>4.006361642765714</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.4330033184045</v>
+        <v>12.43300331840453</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.342392610465986</v>
+        <v>5.342392610465994</v>
       </c>
     </row>
     <row r="5">
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5290484815839135</v>
+        <v>0.5290484815839143</v>
       </c>
       <c r="C5" t="n">
-        <v>0.812109385721111</v>
+        <v>0.8121093857211118</v>
       </c>
       <c r="D5" t="n">
-        <v>0.812109385721111</v>
+        <v>0.8121093857211118</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6613878040517117</v>
+        <v>0.6613878040517122</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5731460622416968</v>
+        <v>0.5731460622416974</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8708039081611664</v>
+        <v>0.8708039081611683</v>
       </c>
       <c r="H5" t="n">
-        <v>0.812109385721111</v>
+        <v>0.8121093857211118</v>
       </c>
       <c r="I5" t="n">
-        <v>0.812109385721111</v>
+        <v>0.8121093857211118</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8123004550132682</v>
+        <v>0.8123004550132684</v>
       </c>
       <c r="K5" t="n">
-        <v>0.812109385721111</v>
+        <v>0.8121093857211118</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8121093857211112</v>
+        <v>0.8121093857211119</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8121093857210039</v>
+        <v>0.8121093857210049</v>
       </c>
       <c r="N5" t="n">
-        <v>2.371762749345276</v>
+        <v>0.5926898299471088</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6529882290408648</v>
+        <v>0.6529882290408661</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6382076344117142</v>
+        <v>0.6382076344117149</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4734205533832452</v>
+        <v>0.473420553383247</v>
       </c>
       <c r="R5" t="n">
-        <v>0.812109385721111</v>
+        <v>0.8121093857211118</v>
       </c>
       <c r="S5" t="n">
-        <v>0.812109385721111</v>
+        <v>0.8121093857211118</v>
       </c>
       <c r="T5" t="n">
-        <v>0.812109385721111</v>
+        <v>0.8121093857211118</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6740188384691606</v>
+        <v>0.6740188384691619</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7356164346703982</v>
+        <v>0.7356164346703986</v>
       </c>
       <c r="W5" t="n">
-        <v>0.812165015258584</v>
+        <v>0.8121650152585851</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4993636476726988</v>
+        <v>0.4993636476726993</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.093666218422088</v>
+        <v>1.093666218422091</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5237904799701834</v>
+        <v>0.5237904799701846</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.812109385721111</v>
+        <v>0.8121093857211118</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.107790169220684</v>
+        <v>1.107790169220686</v>
       </c>
     </row>
     <row r="6">
@@ -3257,82 +3257,82 @@
         <v>2.503508417885572</v>
       </c>
       <c r="C6" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="D6" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="E6" t="n">
-        <v>3.018298389711828</v>
+        <v>3.018298389711829</v>
       </c>
       <c r="F6" t="n">
         <v>1.629954271259621</v>
       </c>
       <c r="G6" t="n">
-        <v>3.172758602498859</v>
+        <v>3.172758602498861</v>
       </c>
       <c r="H6" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="I6" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="J6" t="n">
-        <v>3.172949655886411</v>
+        <v>3.17294965588641</v>
       </c>
       <c r="K6" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="L6" t="n">
         <v>3.172758586594249</v>
       </c>
       <c r="M6" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="N6" t="n">
-        <v>2.371762749345276</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="O6" t="n">
         <v>3.394547237372281</v>
       </c>
       <c r="P6" t="n">
-        <v>3.442782460203671</v>
+        <v>3.442782460203673</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.172758602498859</v>
+        <v>3.172758602498861</v>
       </c>
       <c r="R6" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="S6" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="T6" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="U6" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="V6" t="n">
-        <v>3.945855723497018</v>
+        <v>3.945855723497019</v>
       </c>
       <c r="W6" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="X6" t="n">
         <v>3.172758586594249</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.769260253225695</v>
+        <v>2.769260253225696</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.172758586594248</v>
+        <v>3.172758586594247</v>
       </c>
     </row>
     <row r="7">
@@ -3342,82 +3342,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.143309523682233</v>
+        <v>0.1433095236822328</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.6958603430910324</v>
+        <v>-0.6958603430910315</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2647196033869599</v>
+        <v>-0.2647196033869595</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.579247738562262</v>
+        <v>-0.5792477385622619</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8914914027107095</v>
+        <v>-0.8914914027107086</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08101753914512605</v>
+        <v>0.08101753914512634</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03248116238379792</v>
+        <v>0.03248116238379795</v>
       </c>
       <c r="I7" t="n">
         <v>-0.1135670402527488</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.008232746839726138</v>
+        <v>-0.008232746839726347</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.05247249428355419</v>
+        <v>-0.05247249428355371</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.104960141027596</v>
+        <v>-0.1049601410275976</v>
       </c>
       <c r="M7" t="n">
-        <v>0.006893984883929991</v>
+        <v>0.006893984883930261</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1478947165159418</v>
+        <v>0.1478947165159417</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04914260768797984</v>
+        <v>0.0491426076879801</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01499481658728334</v>
+        <v>0.01499481658728335</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1416568222986244</v>
+        <v>0.1416568222986245</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.2401941131820983</v>
+        <v>-0.240194113182098</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.09422634162257192</v>
+        <v>-0.09422634162257081</v>
       </c>
       <c r="T7" t="n">
-        <v>0.09854265023321157</v>
+        <v>0.0985426502332114</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01255105489634917</v>
+        <v>0.01255105489634955</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.002827696026035962</v>
+        <v>-0.002827696026036641</v>
       </c>
       <c r="W7" t="n">
         <v>0.04818199228869779</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.09266725038255404</v>
+        <v>-0.09266725038255469</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.08253157739441376</v>
+        <v>0.08253157739441386</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.09804900999462175</v>
+        <v>0.09804900999462254</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.08689226769444677</v>
+        <v>-0.08689226769444695</v>
       </c>
       <c r="AB7" t="n">
         <v>0.08978452137307059</v>
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1808310799267723</v>
+        <v>0.1808310799267721</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0577629426426234</v>
+        <v>-0.05776294264262317</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0649797643234527</v>
+        <v>0.06497976432345273</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.04747162558660412</v>
+        <v>-0.04747162558660432</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1122884430480484</v>
+        <v>-0.1122884430480482</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1629696818336894</v>
+        <v>0.1629696818336896</v>
       </c>
       <c r="H8" t="n">
         <v>0.1496609224785224</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1080496587287796</v>
+        <v>0.1080496587287797</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1379249907065073</v>
+        <v>0.1379249907065078</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1252573835165774</v>
+        <v>0.1252573835165777</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1099211935893273</v>
+        <v>0.1099211935893281</v>
       </c>
       <c r="M8" t="n">
         <v>0.1423192512400514</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1822427424924876</v>
+        <v>0.1822427424924879</v>
       </c>
       <c r="O8" t="n">
         <v>0.1537861504358012</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1439551735273801</v>
+        <v>0.1439551735273803</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1804809745142659</v>
+        <v>0.1804809745142661</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0722480078228178</v>
+        <v>0.07224800782281803</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1128312760880434</v>
+        <v>0.1128312760880437</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1682597873317684</v>
+        <v>0.1682597873317689</v>
       </c>
       <c r="U8" t="n">
         <v>0.1434805777196272</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1674903075153072</v>
+        <v>0.1674903075153069</v>
       </c>
       <c r="W8" t="n">
         <v>0.1537394475832353</v>
       </c>
       <c r="X8" t="n">
-        <v>0.113843556852608</v>
+        <v>0.1138435568526082</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1635803020770967</v>
+        <v>0.1635803020770968</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1678639381849933</v>
+        <v>0.167863938184993</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.1152058026090277</v>
+        <v>0.1152058026090279</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1657634096931916</v>
+        <v>0.165763409693192</v>
       </c>
     </row>
   </sheetData>
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1998047942421835</v>
+        <v>0.1998047942421831</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3477434213967868</v>
+        <v>0.3477434213967873</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2539895969842947</v>
+        <v>0.2539895969842957</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2727388747624143</v>
+        <v>0.2727388747624135</v>
       </c>
       <c r="F2" t="n">
-        <v>0.356262882879231</v>
+        <v>0.3562628828792319</v>
       </c>
       <c r="G2" t="n">
         <v>0.2090418874766374</v>
       </c>
       <c r="H2" t="n">
-        <v>0.215275573555167</v>
+        <v>0.2152755735551673</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2268614232079876</v>
+        <v>0.2268614232079882</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2247694535739843</v>
+        <v>0.2247694535739842</v>
       </c>
       <c r="K2" t="n">
-        <v>0.225950085984994</v>
+        <v>0.2259500859849944</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2419999435925996</v>
+        <v>0.2419999435925988</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2303511496140847</v>
+        <v>0.2303511496140851</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1987627370048182</v>
+        <v>0.1987627370048191</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2129127569685036</v>
+        <v>0.2129127569685045</v>
       </c>
       <c r="P2" t="n">
-        <v>0.216489000333528</v>
+        <v>0.2164890003335286</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2017737644536128</v>
+        <v>0.2017737644536132</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2498796873530162</v>
+        <v>0.249879687353017</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2352483101752771</v>
+        <v>0.2352483101752789</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2098314228222196</v>
+        <v>0.2098314228222207</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2131485076724795</v>
+        <v>0.2131485076724803</v>
       </c>
       <c r="V2" t="n">
-        <v>0.26525857618391</v>
+        <v>0.2652585761839105</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2125598157104314</v>
+        <v>0.2125598157104322</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2421291333391546</v>
+        <v>0.2421291333391563</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2070267369340494</v>
+        <v>0.2070267369340487</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2042699283632679</v>
+        <v>0.2042699283632675</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2298238375846768</v>
+        <v>0.2298238375846784</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2094199407975858</v>
+        <v>0.2094199407975859</v>
       </c>
     </row>
     <row r="3">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1589862866132448</v>
+        <v>0.1589862866132454</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="J3" t="n">
         <v>0.1929944903290401</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2323574461600322</v>
+        <v>0.2323574461600324</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1926998960501843</v>
+        <v>0.1926998960501844</v>
       </c>
     </row>
     <row r="4">
@@ -3853,34 +3853,34 @@
         <v>2.170253590472173</v>
       </c>
       <c r="C4" t="n">
-        <v>38.2913864910144</v>
+        <v>38.29138649101438</v>
       </c>
       <c r="D4" t="n">
-        <v>15.95546599874052</v>
+        <v>15.95546599874056</v>
       </c>
       <c r="E4" t="n">
-        <v>27.18605134280405</v>
+        <v>27.18605134280403</v>
       </c>
       <c r="F4" t="n">
-        <v>42.71137352879281</v>
+        <v>42.71137352879287</v>
       </c>
       <c r="G4" t="n">
-        <v>4.272070349933847</v>
+        <v>4.272070349933835</v>
       </c>
       <c r="H4" t="n">
-        <v>6.829406621415441</v>
+        <v>6.829406621415451</v>
       </c>
       <c r="I4" t="n">
-        <v>9.511833498956056</v>
+        <v>9.511833498956062</v>
       </c>
       <c r="J4" t="n">
-        <v>8.291077764982019</v>
+        <v>8.291077764982022</v>
       </c>
       <c r="K4" t="n">
-        <v>8.359863193490261</v>
+        <v>8.359863193490281</v>
       </c>
       <c r="L4" t="n">
-        <v>12.38419559626552</v>
+        <v>12.38419559626553</v>
       </c>
       <c r="M4" t="n">
         <v>10.19194256091454</v>
@@ -3889,43 +3889,43 @@
         <v>2.110777612662494</v>
       </c>
       <c r="O4" t="n">
-        <v>5.08775247345228</v>
+        <v>5.087752473452289</v>
       </c>
       <c r="P4" t="n">
-        <v>5.939694348220312</v>
+        <v>5.939694348220305</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.790344327220385</v>
+        <v>2.790344327220388</v>
       </c>
       <c r="R4" t="n">
         <v>16.08111694085672</v>
       </c>
       <c r="S4" t="n">
-        <v>10.47768539042703</v>
+        <v>10.47768539042704</v>
       </c>
       <c r="T4" t="n">
-        <v>5.10444742122036</v>
+        <v>5.104447421220364</v>
       </c>
       <c r="U4" t="n">
-        <v>5.348202375336969</v>
+        <v>5.348202375336965</v>
       </c>
       <c r="V4" t="n">
-        <v>7.991391632653578</v>
+        <v>7.991391632653597</v>
       </c>
       <c r="W4" t="n">
-        <v>5.579077054546256</v>
+        <v>5.579077054546262</v>
       </c>
       <c r="X4" t="n">
-        <v>12.93899507014301</v>
+        <v>12.938995070143</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.20882166946722</v>
+        <v>4.208821669467207</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.017345609843377</v>
+        <v>3.017345609843381</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.01149134337635</v>
+        <v>10.01149134337636</v>
       </c>
       <c r="AB4" t="n">
         <v>5.183404984265541</v>
@@ -3938,85 +3938,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5183006298406093</v>
+        <v>0.5183006298406085</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7981106257238781</v>
+        <v>0.7981106257238784</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7981106257238781</v>
+        <v>0.7981106257238784</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6491200568038979</v>
+        <v>0.6491200568038998</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5618917569866442</v>
+        <v>0.5618917569866456</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8561310511597161</v>
+        <v>0.8561310511597172</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7981106257238781</v>
+        <v>0.7981106257238784</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7981106257238781</v>
+        <v>0.7981106257238784</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7982944171870112</v>
+        <v>0.7982944171870126</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7981106257238781</v>
+        <v>0.7981106257238784</v>
       </c>
       <c r="L5" t="n">
+        <v>0.7981106257238786</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.7981106257238231</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5812110677117105</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.6408169495396233</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.6262061076258794</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.4633115793102642</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.7981106257238784</v>
       </c>
-      <c r="M5" t="n">
-        <v>0.7981106257238227</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.110777612662494</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.640816949539623</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.62620610762588</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.4633115793102605</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.7981106257238781</v>
-      </c>
       <c r="S5" t="n">
-        <v>0.7981106257238781</v>
+        <v>0.7981106257238784</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7981106257238781</v>
+        <v>0.7981106257238784</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6616769808203652</v>
+        <v>0.6616769808203667</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7225361798248834</v>
+        <v>0.7225361798248841</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7981656163645182</v>
+        <v>0.7981656163645179</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4889567213984604</v>
+        <v>0.4889567213984614</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.076555207489854</v>
+        <v>1.076555207489852</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5131030155167436</v>
+        <v>0.5131030155167432</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.7981106257238781</v>
+        <v>0.7981106257238784</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.090395563715473</v>
+        <v>1.090395563715471</v>
       </c>
     </row>
     <row r="6">
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.252721950401121</v>
+        <v>2.252721950401123</v>
       </c>
       <c r="C6" t="n">
         <v>2.854173312198544</v>
@@ -4035,13 +4035,13 @@
         <v>2.854173312198544</v>
       </c>
       <c r="E6" t="n">
-        <v>2.715360757050377</v>
+        <v>2.715360757050378</v>
       </c>
       <c r="F6" t="n">
         <v>1.467663829504012</v>
       </c>
       <c r="G6" t="n">
-        <v>2.85417326784015</v>
+        <v>2.854173267840149</v>
       </c>
       <c r="H6" t="n">
         <v>2.854173312198544</v>
@@ -4050,28 +4050,28 @@
         <v>2.854173312198544</v>
       </c>
       <c r="J6" t="n">
-        <v>2.854357103661681</v>
+        <v>2.854357103661683</v>
       </c>
       <c r="K6" t="n">
         <v>2.854173312198544</v>
       </c>
       <c r="L6" t="n">
-        <v>2.854173312198544</v>
+        <v>2.854173312198545</v>
       </c>
       <c r="M6" t="n">
         <v>2.854173312198544</v>
       </c>
       <c r="N6" t="n">
-        <v>2.110777612662494</v>
+        <v>2.854173312198544</v>
       </c>
       <c r="O6" t="n">
-        <v>3.053493446907066</v>
+        <v>3.053493446907068</v>
       </c>
       <c r="P6" t="n">
         <v>3.096842166094325</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.85417326784015</v>
+        <v>2.854173267840149</v>
       </c>
       <c r="R6" t="n">
         <v>2.854173312198544</v>
@@ -4092,19 +4092,19 @@
         <v>2.854173312198544</v>
       </c>
       <c r="X6" t="n">
-        <v>2.854173312198544</v>
+        <v>2.854173312198545</v>
       </c>
       <c r="Y6" t="n">
         <v>2.854173312198544</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.491551606562561</v>
+        <v>2.491551606562564</v>
       </c>
       <c r="AA6" t="n">
         <v>2.854173312198544</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.854173312198544</v>
+        <v>2.854173312198545</v>
       </c>
     </row>
     <row r="7">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1417092429723163</v>
+        <v>0.1417092429723174</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.7251214932466701</v>
+        <v>-0.7251214932466697</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.174892161015053</v>
+        <v>-0.1748921610150538</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5192474353127623</v>
+        <v>-0.5192474353127617</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7692433757105283</v>
+        <v>-0.7692433757105276</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0868151623020355</v>
+        <v>0.08681516230203655</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0528271696327307</v>
+        <v>0.05282716963273064</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01559710090737699</v>
+        <v>-0.01559710090737615</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.002672588552226719</v>
+        <v>-0.002672588552227032</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.01093834492375827</v>
+        <v>-0.01093834492375893</v>
       </c>
       <c r="L7" t="n">
         <v>-0.1074207523376055</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03555911213478372</v>
+        <v>-0.03555911213478388</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1484137131639097</v>
+        <v>0.1484137131639107</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06358709083120601</v>
+        <v>0.06358709083120723</v>
       </c>
       <c r="P7" t="n">
-        <v>0.04215448650772706</v>
+        <v>0.04215448650772712</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1308054721105036</v>
+        <v>0.1308054721105034</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1494640829510598</v>
+        <v>-0.1494640829510595</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.06834146467044841</v>
+        <v>-0.06834146467044876</v>
       </c>
       <c r="T7" t="n">
-        <v>0.08383499886820781</v>
+        <v>0.08383499886820645</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06301480632821163</v>
+        <v>0.06301480632821178</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02464859163527163</v>
+        <v>0.02464859163527184</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06683514542374276</v>
+        <v>0.0668351454237428</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1057061124538087</v>
+        <v>-0.1057061124538081</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.09964199823656061</v>
+        <v>0.09964199823656059</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1152314711792707</v>
+        <v>0.115231471179271</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.0348714391992053</v>
+        <v>-0.03487143919920568</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.08620030644610212</v>
+        <v>0.08620030644610246</v>
       </c>
     </row>
     <row r="8">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1766038845941823</v>
+        <v>0.1766038845941845</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0698682356565012</v>
+        <v>-0.06986823565650171</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08673403957323202</v>
+        <v>0.08673403957323277</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.03585963011654581</v>
+        <v>-0.03585963011654691</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.08142437130320899</v>
+        <v>-0.08142437130320901</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1608639961866046</v>
+        <v>0.1608639961866053</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1516330372872947</v>
+        <v>0.1516330372872946</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1320856257891539</v>
+        <v>0.1320856257891543</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1357403091290255</v>
+        <v>0.1357403091290251</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1332940373852803</v>
+        <v>0.1332940373852809</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1054440921483976</v>
+        <v>0.1054440921483969</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1264925734716256</v>
+        <v>0.1264925734716262</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1786123826598754</v>
+        <v>0.178612382659874</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1541660191357727</v>
+        <v>0.1541660191357728</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1479903592319553</v>
+        <v>0.1479903592319557</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1736116043152328</v>
+        <v>0.1736116043152318</v>
       </c>
       <c r="R8" t="n">
-        <v>0.09419398649554787</v>
+        <v>0.09419398649554843</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1164736591579328</v>
+        <v>0.1164736591579335</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1602975476725774</v>
+        <v>0.1602975476725788</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1541413785671226</v>
+        <v>0.1541413785671233</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1707503854462986</v>
+        <v>0.1707503854462989</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1552909530682397</v>
+        <v>0.1552909530682404</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1063534485063157</v>
+        <v>0.1063534485063151</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1646850968709253</v>
+        <v>0.1646850968709252</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1690215481697805</v>
+        <v>0.16902154816978</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.1262781548193921</v>
+        <v>0.1262781548193909</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1609622881336737</v>
+        <v>0.1609622881336742</v>
       </c>
     </row>
   </sheetData>
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.206773327162093</v>
+        <v>0.2067733271620934</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4124787759930909</v>
+        <v>0.4124787759930911</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2778325940107117</v>
+        <v>0.2778325940107127</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3882733264216967</v>
+        <v>0.3882733264216979</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4422840214997525</v>
+        <v>0.4422840214997543</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2169973368675537</v>
+        <v>0.2169973368675538</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2423442428932181</v>
+        <v>0.2423442428932185</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3165488993419392</v>
+        <v>0.3165488993419395</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2508771903780674</v>
+        <v>0.250877190378068</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2675733199596775</v>
+        <v>0.2675733199596772</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2805074131057133</v>
+        <v>0.2805074131057137</v>
       </c>
       <c r="M2" t="n">
-        <v>0.293992520428368</v>
+        <v>0.2939925204283684</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2144413600019928</v>
+        <v>0.2144413600019931</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2294871316206754</v>
+        <v>0.2294871316206757</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2493597884603307</v>
+        <v>0.2493597884603314</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2112374346838425</v>
+        <v>0.2112374346838427</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2787149574166605</v>
+        <v>0.2787149574166608</v>
       </c>
       <c r="S2" t="n">
-        <v>0.303188820329535</v>
+        <v>0.3031888203295353</v>
       </c>
       <c r="T2" t="n">
         <v>0.2229953126522587</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2422332996043769</v>
+        <v>0.2422332996043772</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2885841628277003</v>
+        <v>0.2885841628276995</v>
       </c>
       <c r="W2" t="n">
-        <v>0.241232009033954</v>
+        <v>0.2412320090339553</v>
       </c>
       <c r="X2" t="n">
-        <v>0.257218526012898</v>
+        <v>0.2572185260128984</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2253922050654535</v>
+        <v>0.2253922050654536</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2211342309432686</v>
+        <v>0.2211342309432687</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2833615413453145</v>
+        <v>0.2833615413453147</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2596436648613531</v>
+        <v>0.2596436648613532</v>
       </c>
     </row>
     <row r="3">
@@ -4534,85 +4534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2020121953889805</v>
+        <v>0.2020121953889826</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2059384697833892</v>
+        <v>0.205938469783389</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2454247786757228</v>
+        <v>0.2454247786757223</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2054128994054842</v>
+        <v>0.2054128994054834</v>
       </c>
     </row>
     <row r="4">
@@ -4622,25 +4622,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.971016133399253</v>
+        <v>0.971016133399255</v>
       </c>
       <c r="C4" t="n">
-        <v>56.68747328479408</v>
+        <v>56.687473284794</v>
       </c>
       <c r="D4" t="n">
-        <v>20.91190763582138</v>
+        <v>20.91190763582139</v>
       </c>
       <c r="E4" t="n">
-        <v>50.7293337900852</v>
+        <v>50.72933379008519</v>
       </c>
       <c r="F4" t="n">
-        <v>66.25833053245083</v>
+        <v>66.2583305324508</v>
       </c>
       <c r="G4" t="n">
-        <v>3.40399002634791</v>
+        <v>3.403990026347909</v>
       </c>
       <c r="H4" t="n">
-        <v>11.49679317470534</v>
+        <v>11.49679317470535</v>
       </c>
       <c r="I4" t="n">
         <v>32.19691177771759</v>
@@ -4649,25 +4649,25 @@
         <v>12.24166292050029</v>
       </c>
       <c r="K4" t="n">
-        <v>16.42573244208239</v>
+        <v>16.42573244208238</v>
       </c>
       <c r="L4" t="n">
         <v>18.43933648553143</v>
       </c>
       <c r="M4" t="n">
-        <v>23.37432405171801</v>
+        <v>23.37432405171802</v>
       </c>
       <c r="N4" t="n">
-        <v>3.054452608428307</v>
+        <v>3.054452608428304</v>
       </c>
       <c r="O4" t="n">
-        <v>6.395119605427611</v>
+        <v>6.395119605427607</v>
       </c>
       <c r="P4" t="n">
-        <v>11.73351816356337</v>
+        <v>11.7335181635634</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.190734241826713</v>
+        <v>2.190734241826714</v>
       </c>
       <c r="R4" t="n">
         <v>22.00099431177849</v>
@@ -4676,31 +4676,31 @@
         <v>22.27895625369885</v>
       </c>
       <c r="T4" t="n">
-        <v>5.414198871094561</v>
+        <v>5.414198871094552</v>
       </c>
       <c r="U4" t="n">
-        <v>10.08302575697507</v>
+        <v>10.08302575697509</v>
       </c>
       <c r="V4" t="n">
-        <v>11.26134615183621</v>
+        <v>11.2613461518362</v>
       </c>
       <c r="W4" t="n">
-        <v>10.36069885671897</v>
+        <v>10.36069885671899</v>
       </c>
       <c r="X4" t="n">
-        <v>14.94628395400539</v>
+        <v>14.94628395400541</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.996410359193185</v>
+        <v>5.996410359193176</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.42065302242989</v>
+        <v>4.420653022429888</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.75691507348998</v>
+        <v>21.75691507348996</v>
       </c>
       <c r="AB4" t="n">
-        <v>16.18766568518601</v>
+        <v>16.18766568518599</v>
       </c>
     </row>
     <row r="5">
@@ -4710,85 +4710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5824809145830688</v>
+        <v>0.5824809145830708</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8962819278105941</v>
+        <v>0.8962819278105971</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8962819278105941</v>
+        <v>0.8962819278105971</v>
       </c>
       <c r="E5" t="n">
-        <v>0.729192144828043</v>
+        <v>0.7291921448280416</v>
       </c>
       <c r="F5" t="n">
-        <v>0.631367444969569</v>
+        <v>0.6313674449695703</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9613506121233627</v>
+        <v>0.9613506121233616</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8962819278105941</v>
+        <v>0.8962819278105971</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8962819278105941</v>
+        <v>0.8962819278105971</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8965031112682836</v>
+        <v>0.8965031112682829</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8962819278105941</v>
+        <v>0.8962819278105971</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8962819278105941</v>
+        <v>0.8962819278105953</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8962819278105191</v>
+        <v>0.8962819278105221</v>
       </c>
       <c r="N5" t="n">
-        <v>3.054452608428307</v>
+        <v>0.6530336447826113</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7198803850252922</v>
+        <v>0.7198803850252926</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7034946337506446</v>
+        <v>0.7034946337506461</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.520811853338573</v>
+        <v>0.5208118533385742</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8962819278105941</v>
+        <v>0.8962819278105971</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8962819278105941</v>
+        <v>0.8962819278105971</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8962819278105941</v>
+        <v>0.8962819278105971</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7432040430256855</v>
+        <v>0.7432040430256863</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8116027526324898</v>
+        <v>0.8116027526324889</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8963435986567697</v>
+        <v>0.8963435986567723</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5495723397055038</v>
+        <v>0.5495723397055035</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.208431177017178</v>
+        <v>1.208431177017179</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.576651899661482</v>
+        <v>0.5766518996614804</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.8962819278105941</v>
+        <v>0.8962819278105971</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.22407332569759</v>
+        <v>1.224073325697588</v>
       </c>
     </row>
     <row r="6">
@@ -4798,85 +4798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.995993260072042</v>
+        <v>2.995993260072043</v>
       </c>
       <c r="C6" t="n">
-        <v>3.800045570772968</v>
+        <v>3.800045570772971</v>
       </c>
       <c r="D6" t="n">
-        <v>3.800045570772968</v>
+        <v>3.800045570772971</v>
       </c>
       <c r="E6" t="n">
-        <v>3.614473414409089</v>
+        <v>3.614473414409093</v>
       </c>
       <c r="F6" t="n">
         <v>1.94648582403894</v>
       </c>
       <c r="G6" t="n">
-        <v>3.800045359224868</v>
+        <v>3.800045359224869</v>
       </c>
       <c r="H6" t="n">
-        <v>3.800045570772968</v>
+        <v>3.800045570772971</v>
       </c>
       <c r="I6" t="n">
-        <v>3.800045570772968</v>
+        <v>3.800045570772971</v>
       </c>
       <c r="J6" t="n">
-        <v>3.800266754230647</v>
+        <v>3.80026675423065</v>
       </c>
       <c r="K6" t="n">
-        <v>3.800045570772968</v>
+        <v>3.800045570772971</v>
       </c>
       <c r="L6" t="n">
-        <v>3.800045570772968</v>
+        <v>3.800045570772971</v>
       </c>
       <c r="M6" t="n">
-        <v>3.800045570772968</v>
+        <v>3.800045570772971</v>
       </c>
       <c r="N6" t="n">
-        <v>3.054452608428307</v>
+        <v>3.800045570772971</v>
       </c>
       <c r="O6" t="n">
-        <v>4.06650717206867</v>
+        <v>4.066507172068677</v>
       </c>
       <c r="P6" t="n">
-        <v>4.124458044645884</v>
+        <v>4.124458044645889</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.800045359224868</v>
+        <v>3.800045359224869</v>
       </c>
       <c r="R6" t="n">
-        <v>3.800045570772968</v>
+        <v>3.800045570772971</v>
       </c>
       <c r="S6" t="n">
-        <v>3.800045570772968</v>
+        <v>3.800045570772971</v>
       </c>
       <c r="T6" t="n">
-        <v>3.800045570772968</v>
+        <v>3.800045570772971</v>
       </c>
       <c r="U6" t="n">
-        <v>3.800045570772968</v>
+        <v>3.800045570772971</v>
       </c>
       <c r="V6" t="n">
         <v>4.728898242869422</v>
       </c>
       <c r="W6" t="n">
-        <v>3.800045570772968</v>
+        <v>3.800045570772971</v>
       </c>
       <c r="X6" t="n">
-        <v>3.800045570772968</v>
+        <v>3.800045570772971</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.800045570772968</v>
+        <v>3.800045570772971</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.3152734425383</v>
+        <v>3.315273442538305</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.800045570772968</v>
+        <v>3.800045570772971</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.800045570772968</v>
+        <v>3.800045570772971</v>
       </c>
     </row>
     <row r="7">
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1878951724583454</v>
+        <v>0.1878951724583448</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.018176199131164</v>
+        <v>-1.018176199131165</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2280643852345013</v>
+        <v>-0.2280643852344998</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9083230188639746</v>
+        <v>-0.9083230188639738</v>
       </c>
       <c r="F7" t="n">
         <v>-1.184527224409174</v>
       </c>
       <c r="G7" t="n">
-        <v>0.127114418024437</v>
+        <v>0.1271144180244366</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.01866773690810263</v>
+        <v>-0.01866773690810202</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4536101110312368</v>
+        <v>-0.4536101110312362</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.06799565690286351</v>
+        <v>-0.06799565690286273</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1684999475916447</v>
+        <v>-0.1684999475916437</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.247897930253385</v>
+        <v>-0.2478979302533854</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3207168168595316</v>
+        <v>-0.3207168168595322</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1429881048694076</v>
+        <v>0.1429881048694072</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05260041146112801</v>
+        <v>0.05260041146112784</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.06599523535174708</v>
+        <v>-0.06599523535174656</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1619074789944248</v>
+        <v>0.1619074789944243</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.2315038305211122</v>
+        <v>-0.231503830521111</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.383871790401714</v>
+        <v>-0.3838717904017143</v>
       </c>
       <c r="T7" t="n">
-        <v>0.09321810441729214</v>
+        <v>0.09321810441729209</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.02185435192661858</v>
+        <v>-0.02185435192661732</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.02387932160722741</v>
+        <v>-0.02387932160722804</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.01533886032758341</v>
+        <v>-0.01533886032758427</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1076178928738237</v>
+        <v>-0.1076178928738234</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.07835304234844831</v>
+        <v>0.07835304234844909</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1025738998250362</v>
+        <v>0.1025738998250353</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.2636046750217186</v>
+        <v>-0.2636046750217184</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.1214474816262761</v>
+        <v>-0.1214474816262773</v>
       </c>
     </row>
     <row r="8">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1988027055754614</v>
+        <v>0.1988027055754618</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1442581631881799</v>
+        <v>-0.1442581631881801</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08059904808937846</v>
+        <v>0.08059904808937884</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1169327344917766</v>
+        <v>-0.1169327344917752</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1901431643122705</v>
+        <v>-0.1901431643122708</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1813712783167225</v>
+        <v>0.1813712783167226</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1403868392679194</v>
+        <v>0.1403868392679191</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01669132941150901</v>
+        <v>0.01669132941150955</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1262362897595589</v>
+        <v>0.1262362897595588</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09744178298644139</v>
+        <v>0.0974417829864429</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07424954099502802</v>
+        <v>0.07424954099502851</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05460182285186429</v>
+        <v>0.05460182285186427</v>
       </c>
       <c r="N8" t="n">
         <v>0.1860378795520613</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1599569626214886</v>
+        <v>0.1599569626214893</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1258682222193847</v>
+        <v>0.1258682222193855</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1914423297532611</v>
+        <v>0.1914423297532617</v>
       </c>
       <c r="R8" t="n">
-        <v>0.07991645292905772</v>
+        <v>0.07991645292905766</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03506240852838077</v>
+        <v>0.0350624085283805</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1719463233890358</v>
+        <v>0.1719463233890342</v>
       </c>
       <c r="U8" t="n">
-        <v>0.138825975990514</v>
+        <v>0.1388259759905148</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1660499389777123</v>
+        <v>0.1660499389777119</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1407892548612906</v>
+        <v>0.1407892548612918</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1147885179558686</v>
+        <v>0.114788517955868</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1675795651887639</v>
+        <v>0.1675795651887643</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1743421584057186</v>
+        <v>0.174342158405719</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.06995705031061328</v>
+        <v>0.06995705031061263</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1109211498496724</v>
+        <v>0.1109211498496726</v>
       </c>
     </row>
   </sheetData>
@@ -5218,85 +5218,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1927433843967206</v>
+        <v>0.1927433843967203</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3557055697200878</v>
+        <v>0.3557055697200874</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2308250273011266</v>
+        <v>0.2308250273011263</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2700783125856377</v>
+        <v>0.2700783125856375</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3785441743156339</v>
+        <v>0.3785441743156333</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1998972606851142</v>
+        <v>0.1998972606851135</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2190767992039412</v>
+        <v>0.2190767992039408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2400180120021616</v>
+        <v>0.2400180120021614</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2255194596601567</v>
+        <v>0.2255194596601562</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2249993937734924</v>
+        <v>0.2249993937734921</v>
       </c>
       <c r="L2" t="n">
-        <v>0.22985756836513</v>
+        <v>0.2298575683651299</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2454245788097375</v>
+        <v>0.2454245788097372</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1999953202691273</v>
+        <v>0.1999953202691271</v>
       </c>
       <c r="O2" t="n">
-        <v>0.216441325253563</v>
+        <v>0.2164413252535627</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2322805305443723</v>
+        <v>0.2322805305443721</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1945009008370469</v>
+        <v>0.1945009008370467</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2374703502402263</v>
+        <v>0.2374703502402261</v>
       </c>
       <c r="S2" t="n">
         <v>0.255547398036072</v>
       </c>
       <c r="T2" t="n">
-        <v>0.204656432746398</v>
+        <v>0.2046564327463976</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2238489347334139</v>
+        <v>0.2238489347334136</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2680468347198613</v>
+        <v>0.2680468347198616</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2155506998882493</v>
+        <v>0.2155506998882492</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2362909803459963</v>
+        <v>0.2362909803459961</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2061152847881989</v>
+        <v>0.2061152847881986</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1994246400354061</v>
+        <v>0.1994246400354057</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2226560017923065</v>
+        <v>0.2226560017923061</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2276640925449544</v>
+        <v>0.2276640925449541</v>
       </c>
     </row>
     <row r="3">
@@ -5306,85 +5306,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="E3" t="n">
         <v>0.1573295684172114</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1917572205200052</v>
+        <v>0.1917572205200051</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="V3" t="n">
-        <v>0.232634172964947</v>
+        <v>0.2326341729649459</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1911640462128524</v>
+        <v>0.1911640462128522</v>
       </c>
     </row>
     <row r="4">
@@ -5394,85 +5394,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9033017085107243</v>
+        <v>0.9033017085107253</v>
       </c>
       <c r="C4" t="n">
-        <v>40.60070057057431</v>
+        <v>40.60070057057429</v>
       </c>
       <c r="D4" t="n">
-        <v>10.25450357128949</v>
+        <v>10.25450357128948</v>
       </c>
       <c r="E4" t="n">
-        <v>28.48472500155237</v>
+        <v>28.48472500155238</v>
       </c>
       <c r="F4" t="n">
-        <v>47.55623343661007</v>
+        <v>47.55623343661005</v>
       </c>
       <c r="G4" t="n">
-        <v>2.462035395250112</v>
+        <v>2.462035395250117</v>
       </c>
       <c r="H4" t="n">
-        <v>8.09817996654674</v>
+        <v>8.098179966546741</v>
       </c>
       <c r="I4" t="n">
-        <v>13.09252432252512</v>
+        <v>13.0925243225251</v>
       </c>
       <c r="J4" t="n">
-        <v>8.436279228728003</v>
+        <v>8.436279228728008</v>
       </c>
       <c r="K4" t="n">
-        <v>8.377596710059725</v>
+        <v>8.377596710059729</v>
       </c>
       <c r="L4" t="n">
-        <v>8.299848650623582</v>
+        <v>8.299848650623566</v>
       </c>
       <c r="M4" t="n">
-        <v>12.66438378909965</v>
+        <v>12.66438378909963</v>
       </c>
       <c r="N4" t="n">
-        <v>2.70898580885033</v>
+        <v>2.708985808850324</v>
       </c>
       <c r="O4" t="n">
-        <v>6.150794270406331</v>
+        <v>6.15079427040634</v>
       </c>
       <c r="P4" t="n">
-        <v>10.05470845690709</v>
+        <v>10.0547084569071</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.341524663502676</v>
+        <v>1.341524663502674</v>
       </c>
       <c r="R4" t="n">
-        <v>12.72238931335213</v>
+        <v>12.72238931335212</v>
       </c>
       <c r="S4" t="n">
         <v>14.01527453912938</v>
       </c>
       <c r="T4" t="n">
-        <v>3.896081733585989</v>
+        <v>3.896081733585983</v>
       </c>
       <c r="U4" t="n">
-        <v>7.487522895414781</v>
+        <v>7.487522895414775</v>
       </c>
       <c r="V4" t="n">
-        <v>8.491176369987322</v>
+        <v>8.491176369987327</v>
       </c>
       <c r="W4" t="n">
-        <v>6.365289542635971</v>
+        <v>6.365289542635969</v>
       </c>
       <c r="X4" t="n">
-        <v>11.4682400195804</v>
+        <v>11.46824001958042</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.324884011692818</v>
+        <v>4.324884011692815</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.384388404623832</v>
+        <v>2.384388404623828</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.489837856310526</v>
+        <v>8.489837856310542</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.879890428395848</v>
+        <v>9.879890428395852</v>
       </c>
     </row>
     <row r="5">
@@ -5482,85 +5482,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5156710562532825</v>
+        <v>0.5156710562532807</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7929377833557667</v>
+        <v>0.7929377833557636</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7929377833557667</v>
+        <v>0.7929377833557636</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6453014300394702</v>
+        <v>0.6453014300394675</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5588659718473252</v>
+        <v>0.5588659718473237</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8504308454421331</v>
+        <v>0.8504308454421295</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7929377833557667</v>
+        <v>0.7929377833557636</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7929377833557667</v>
+        <v>0.7929377833557636</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7931821946132556</v>
+        <v>0.7931821946132519</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7929377833557667</v>
+        <v>0.7929377833557636</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7929377833557667</v>
+        <v>0.7929377833557636</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7929377833557605</v>
+        <v>0.7929377833557567</v>
       </c>
       <c r="N5" t="n">
-        <v>2.70898580885033</v>
+        <v>0.578009684128737</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6370737919654395</v>
+        <v>0.6370737919654358</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6225957519479772</v>
+        <v>0.6225957519479747</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4611818160852111</v>
+        <v>0.4611818160852098</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7929377833557667</v>
+        <v>0.7929377833557636</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7929377833557667</v>
+        <v>0.7929377833557636</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7929377833557667</v>
+        <v>0.7929377833557636</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6577032085521852</v>
+        <v>0.6577032085521829</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7184002328818813</v>
+        <v>0.718400232881878</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7929922741727996</v>
+        <v>0.7929922741727973</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4865938625370831</v>
+        <v>0.4865938625370811</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.068781346976838</v>
+        <v>1.068781346976835</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5105206844526159</v>
+        <v>0.5105206844526136</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.7929377833557667</v>
+        <v>0.7929377833557636</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.08256606444273</v>
+        <v>1.082566064442726</v>
       </c>
     </row>
     <row r="6">
@@ -5570,13 +5570,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.449760081864289</v>
+        <v>2.44976008186429</v>
       </c>
       <c r="C6" t="n">
-        <v>3.105323695045693</v>
+        <v>3.105323695045695</v>
       </c>
       <c r="D6" t="n">
-        <v>3.105323695045693</v>
+        <v>3.105323695045695</v>
       </c>
       <c r="E6" t="n">
         <v>2.954022175555437</v>
@@ -5585,70 +5585,70 @@
         <v>1.594070835689823</v>
       </c>
       <c r="G6" t="n">
-        <v>3.10532355000852</v>
+        <v>3.105323550008523</v>
       </c>
       <c r="H6" t="n">
-        <v>3.105323695045693</v>
+        <v>3.105323695045695</v>
       </c>
       <c r="I6" t="n">
-        <v>3.105323695045693</v>
+        <v>3.105323695045695</v>
       </c>
       <c r="J6" t="n">
-        <v>3.105568106303182</v>
+        <v>3.10556810630318</v>
       </c>
       <c r="K6" t="n">
-        <v>3.105323695045693</v>
+        <v>3.105323695045695</v>
       </c>
       <c r="L6" t="n">
-        <v>3.105323695045693</v>
+        <v>3.105323695045695</v>
       </c>
       <c r="M6" t="n">
-        <v>3.105323695045693</v>
+        <v>3.105323695045695</v>
       </c>
       <c r="N6" t="n">
-        <v>2.70898580885033</v>
+        <v>3.105323695045695</v>
       </c>
       <c r="O6" t="n">
         <v>3.322576424965308</v>
       </c>
       <c r="P6" t="n">
-        <v>3.369825197835384</v>
+        <v>3.369825197835381</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.10532355000852</v>
+        <v>3.105323550008523</v>
       </c>
       <c r="R6" t="n">
-        <v>3.105323695045693</v>
+        <v>3.105323695045695</v>
       </c>
       <c r="S6" t="n">
-        <v>3.105323695045693</v>
+        <v>3.105323695045695</v>
       </c>
       <c r="T6" t="n">
-        <v>3.105323695045693</v>
+        <v>3.105323695045695</v>
       </c>
       <c r="U6" t="n">
-        <v>3.105323695045693</v>
+        <v>3.105323695045695</v>
       </c>
       <c r="V6" t="n">
-        <v>3.862967536629708</v>
+        <v>3.862967536629706</v>
       </c>
       <c r="W6" t="n">
-        <v>3.105323695045693</v>
+        <v>3.105323695045695</v>
       </c>
       <c r="X6" t="n">
-        <v>3.105323695045693</v>
+        <v>3.105323695045695</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.105323695045693</v>
+        <v>3.105323695045695</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.710077073695882</v>
+        <v>2.710077073695883</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.105323695045693</v>
+        <v>3.105323695045695</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.105323695045693</v>
+        <v>3.105323695045695</v>
       </c>
     </row>
     <row r="7">
@@ -5658,85 +5658,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1731267755296898</v>
+        <v>0.1731267755296893</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.782276959835106</v>
+        <v>-0.7822769598351059</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.04965746642822033</v>
+        <v>-0.04965746642822082</v>
       </c>
       <c r="E7" t="n">
         <v>-0.5148818027473543</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9095288613215819</v>
+        <v>-0.9095288613215815</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1306009060254587</v>
+        <v>0.1306009060254599</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02031915528139824</v>
+        <v>0.02031915528139791</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.102953783778761</v>
+        <v>-0.1029537837787615</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.01544317598277569</v>
+        <v>-0.01544317598277559</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.01582688513986897</v>
+        <v>-0.01582688513986914</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0461721648686688</v>
+        <v>-0.04617216486866924</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1339357926569604</v>
+        <v>-0.1339357926569602</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1306730433410584</v>
+        <v>0.1306730433410583</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03197028725102986</v>
+        <v>0.03197028725102963</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.06258784838819435</v>
+        <v>-0.06258784838819467</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1630401260471985</v>
+        <v>0.1630401260471983</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.08747977498462699</v>
+        <v>-0.08747977498462732</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1992954640021894</v>
+        <v>-0.1992954640021896</v>
       </c>
       <c r="T7" t="n">
         <v>0.1036815802127496</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.01085171584137904</v>
+        <v>-0.01085171584137921</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01000542900372628</v>
+        <v>0.01000542900372514</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03866285795812324</v>
+        <v>0.03866285795812276</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0819371271832622</v>
+        <v>-0.08193712718326238</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.09450702545219875</v>
+        <v>0.09450702545219836</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1334430144902994</v>
+        <v>0.1334430144902991</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.003114292657539357</v>
+        <v>-0.003114292657539414</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.03109142511493666</v>
+        <v>-0.03109142511493672</v>
       </c>
     </row>
     <row r="8">
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1845363687545104</v>
+        <v>0.1845363687545102</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0872131902041553</v>
+        <v>-0.08721319020415531</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1212504715968138</v>
+        <v>0.1212504715968134</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.03578000350477419</v>
+        <v>-0.03578000350477414</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1222746063127031</v>
+        <v>-0.1222746063127036</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1723408388965729</v>
+        <v>0.1723408388965734</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1413418293797659</v>
+        <v>0.1413418293797654</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1061934620580672</v>
+        <v>0.1061934620580669</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1312426189429065</v>
+        <v>0.1312426189429061</v>
       </c>
       <c r="K8" t="n">
         <v>0.1308178603670449</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1218688359774104</v>
+        <v>0.1218688359774102</v>
       </c>
       <c r="M8" t="n">
-        <v>0.09750311609225779</v>
+        <v>0.09750311609225767</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1724717211890735</v>
+        <v>0.1724717211890729</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1440076576055253</v>
+        <v>0.1440076576055251</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1168226098415884</v>
+        <v>0.1168226098415883</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1817044275360584</v>
+        <v>0.1817044275360583</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1106865236102028</v>
+        <v>0.1106865236102023</v>
       </c>
       <c r="S8" t="n">
-        <v>0.07788707656759979</v>
+        <v>0.07788707656759943</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1648516319262734</v>
+        <v>0.1648516319262732</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1319311192127026</v>
+        <v>0.1319311192127024</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1667500467417948</v>
+        <v>0.1667500467417949</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1461621732398964</v>
+        <v>0.1461621732398961</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1120290761289642</v>
+        <v>0.112029076128964</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1621360323144523</v>
+        <v>0.1621360323144522</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1731613866556299</v>
+        <v>0.1731613866556296</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.134258738477947</v>
+        <v>0.1342587384779465</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1265371448046487</v>
+        <v>0.1265371448046482</v>
       </c>
     </row>
   </sheetData>
@@ -5990,85 +5990,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1809635165992374</v>
+        <v>0.1809635165992373</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3254187557618639</v>
+        <v>0.3254187557618637</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2109285276834775</v>
+        <v>0.2109285276834772</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1692468211587366</v>
+        <v>0.1692468211587367</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3374218608611602</v>
+        <v>0.3374218608611599</v>
       </c>
       <c r="G2" t="n">
-        <v>0.183660306424082</v>
+        <v>0.1836603064240818</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2007002832348359</v>
+        <v>0.2007002832348355</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2018487544897591</v>
+        <v>0.2018487544897589</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2046707891973144</v>
+        <v>0.2046707891973142</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2001528985125422</v>
+        <v>0.2001528985125421</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2133143586880618</v>
+        <v>0.2133143586880616</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2177736756580187</v>
+        <v>0.2177736756580184</v>
       </c>
       <c r="N2" t="n">
-        <v>0.184221713332071</v>
+        <v>0.1842217133320706</v>
       </c>
       <c r="O2" t="n">
         <v>0.2002231652762052</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2163628700488301</v>
+        <v>0.21636287004883</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1806992486490646</v>
+        <v>0.1806992486490644</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2092926138403313</v>
+        <v>0.2092926138403312</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2277800496836788</v>
+        <v>0.2277800496836784</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1901210749489645</v>
+        <v>0.1901210749489647</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2047914916885308</v>
+        <v>0.2047914916885306</v>
       </c>
       <c r="V2" t="n">
         <v>0.2429565163503864</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1920449123638216</v>
+        <v>0.1920449123638213</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2149304063598473</v>
+        <v>0.2149304063598469</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.189627848201731</v>
+        <v>0.1896278482017307</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1823102404925616</v>
+        <v>0.1823102404925615</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1917170460002907</v>
+        <v>0.1917170460002909</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1993138869871731</v>
+        <v>0.1993138869871729</v>
       </c>
     </row>
     <row r="3">
@@ -6087,7 +6087,7 @@
         <v>0.1786496520622533</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1193062416870888</v>
+        <v>0.1193062416870886</v>
       </c>
       <c r="F3" t="n">
         <v>0.1786496520622533</v>
@@ -6102,7 +6102,7 @@
         <v>0.1786496520622533</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1790531092005284</v>
+        <v>0.1790531092005279</v>
       </c>
       <c r="K3" t="n">
         <v>0.1786496520622533</v>
@@ -6169,55 +6169,55 @@
         <v>1.030222523812147</v>
       </c>
       <c r="C4" t="n">
-        <v>36.70722954718246</v>
+        <v>36.70722954718251</v>
       </c>
       <c r="D4" t="n">
-        <v>8.586669075091676</v>
+        <v>8.586669075091672</v>
       </c>
       <c r="E4" t="n">
-        <v>11.92300920188534</v>
+        <v>11.92300920188533</v>
       </c>
       <c r="F4" t="n">
-        <v>41.48094442347794</v>
+        <v>41.48094442347801</v>
       </c>
       <c r="G4" t="n">
-        <v>1.65180475717767</v>
+        <v>1.651804757177679</v>
       </c>
       <c r="H4" t="n">
-        <v>6.418902112942513</v>
+        <v>6.41890211294251</v>
       </c>
       <c r="I4" t="n">
-        <v>6.551099088195406</v>
+        <v>6.551099088195399</v>
       </c>
       <c r="J4" t="n">
-        <v>6.71952681689547</v>
+        <v>6.719526816895476</v>
       </c>
       <c r="K4" t="n">
-        <v>5.716312141722086</v>
+        <v>5.716312141722087</v>
       </c>
       <c r="L4" t="n">
         <v>7.958227430927804</v>
       </c>
       <c r="M4" t="n">
-        <v>10.1309253408272</v>
+        <v>10.13092534082721</v>
       </c>
       <c r="N4" t="n">
         <v>1.896691392978791</v>
       </c>
       <c r="O4" t="n">
-        <v>5.313289812957473</v>
+        <v>5.313289812957466</v>
       </c>
       <c r="P4" t="n">
-        <v>8.979815792654623</v>
+        <v>8.979815792654612</v>
       </c>
       <c r="Q4" t="n">
         <v>1.014773836019429</v>
       </c>
       <c r="R4" t="n">
-        <v>8.668157269198126</v>
+        <v>8.668157269198124</v>
       </c>
       <c r="S4" t="n">
-        <v>11.50035560847022</v>
+        <v>11.50035560847021</v>
       </c>
       <c r="T4" t="n">
         <v>3.444432233543373</v>
@@ -6226,16 +6226,16 @@
         <v>6.286473446484306</v>
       </c>
       <c r="V4" t="n">
-        <v>6.278798787988451</v>
+        <v>6.278798787988458</v>
       </c>
       <c r="W4" t="n">
-        <v>3.764335982432331</v>
+        <v>3.764335982432334</v>
       </c>
       <c r="X4" t="n">
-        <v>9.151098556417411</v>
+        <v>9.151098556417415</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.305870450394919</v>
+        <v>3.305870450394927</v>
       </c>
       <c r="Z4" t="n">
         <v>1.314129338574281</v>
@@ -6244,7 +6244,7 @@
         <v>3.806572321643929</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.041585181590169</v>
+        <v>6.041585181590162</v>
       </c>
     </row>
     <row r="5">
@@ -6254,70 +6254,70 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4873134387416395</v>
+        <v>0.4873134387416397</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7532382498825948</v>
+        <v>0.7532382498825942</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7532382498825948</v>
+        <v>0.7532382498825942</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6116411322490577</v>
+        <v>0.6116411322490565</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5287414163852174</v>
+        <v>0.5287414163852171</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8083794918089184</v>
+        <v>0.8083794918089187</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7532382498825948</v>
+        <v>0.7532382498825942</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7532382498825948</v>
+        <v>0.7532382498825942</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7534502020917312</v>
+        <v>0.7534502020917314</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7532382498825948</v>
+        <v>0.7532382498825942</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7532382498825948</v>
+        <v>0.7532382498825942</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7532382498826532</v>
+        <v>0.7532382498826534</v>
       </c>
       <c r="N5" t="n">
-        <v>1.896691392978792</v>
+        <v>0.5471020329879894</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6037500552232883</v>
+        <v>0.6037500552232877</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5898642561672964</v>
+        <v>0.5898642561672954</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4350531439253916</v>
+        <v>0.4350531439253917</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7532382498825948</v>
+        <v>0.7532382498825942</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7532382498825948</v>
+        <v>0.7532382498825942</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7532382498825948</v>
+        <v>0.7532382498825942</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6235015415632308</v>
+        <v>0.6235015415632307</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6815475812853039</v>
+        <v>0.6815475812853041</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7532905116923753</v>
+        <v>0.753290511692375</v>
       </c>
       <c r="X5" t="n">
         <v>0.4594256812452377</v>
@@ -6326,13 +6326,13 @@
         <v>1.017739846741752</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.4823737488524855</v>
+        <v>0.4823737488524854</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.7532382498825948</v>
+        <v>0.7532382498825942</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.031018951356144</v>
+        <v>1.031018951356145</v>
       </c>
     </row>
     <row r="6">
@@ -6342,85 +6342,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.179572844425893</v>
+        <v>2.179572844425891</v>
       </c>
       <c r="C6" t="n">
-        <v>2.763320625620718</v>
+        <v>2.763320625620715</v>
       </c>
       <c r="D6" t="n">
-        <v>2.763320625620718</v>
+        <v>2.763320625620715</v>
       </c>
       <c r="E6" t="n">
-        <v>2.628593917702822</v>
+        <v>2.62859391770282</v>
       </c>
       <c r="F6" t="n">
-        <v>1.41762284160818</v>
+        <v>1.417622841608178</v>
       </c>
       <c r="G6" t="n">
         <v>2.763320494209698</v>
       </c>
       <c r="H6" t="n">
-        <v>2.763320625620718</v>
+        <v>2.763320625620715</v>
       </c>
       <c r="I6" t="n">
-        <v>2.763320625620718</v>
+        <v>2.763320625620715</v>
       </c>
       <c r="J6" t="n">
-        <v>2.763532577829857</v>
+        <v>2.763532577829854</v>
       </c>
       <c r="K6" t="n">
-        <v>2.763320625620718</v>
+        <v>2.763320625620715</v>
       </c>
       <c r="L6" t="n">
-        <v>2.763320625620718</v>
+        <v>2.763320625620715</v>
       </c>
       <c r="M6" t="n">
-        <v>2.763320625620718</v>
+        <v>2.763320625620715</v>
       </c>
       <c r="N6" t="n">
-        <v>1.896691392978791</v>
+        <v>2.763320625620715</v>
       </c>
       <c r="O6" t="n">
-        <v>2.95677370099665</v>
+        <v>2.956773700996648</v>
       </c>
       <c r="P6" t="n">
-        <v>2.998846454373321</v>
+        <v>2.998846454373318</v>
       </c>
       <c r="Q6" t="n">
         <v>2.763320494209698</v>
       </c>
       <c r="R6" t="n">
-        <v>2.763320625620718</v>
+        <v>2.763320625620715</v>
       </c>
       <c r="S6" t="n">
-        <v>2.763320625620718</v>
+        <v>2.763320625620715</v>
       </c>
       <c r="T6" t="n">
-        <v>2.763320625620718</v>
+        <v>2.763320625620715</v>
       </c>
       <c r="U6" t="n">
-        <v>2.763320625620718</v>
+        <v>2.763320625620715</v>
       </c>
       <c r="V6" t="n">
-        <v>3.437879449749056</v>
+        <v>3.437879449749054</v>
       </c>
       <c r="W6" t="n">
-        <v>2.763320625620718</v>
+        <v>2.763320625620715</v>
       </c>
       <c r="X6" t="n">
-        <v>2.763320625620718</v>
+        <v>2.763320625620715</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.763320625620718</v>
+        <v>2.763320625620715</v>
       </c>
       <c r="Z6" t="n">
         <v>2.411372570256661</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.763320625620718</v>
+        <v>2.763320625620715</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.763320625620718</v>
+        <v>2.763320625620715</v>
       </c>
     </row>
     <row r="7">
@@ -6433,82 +6433,82 @@
         <v>0.1568953990031617</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.6899246819947973</v>
+        <v>-0.6899246819947971</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.01828826560719604</v>
+        <v>-0.01828826560719592</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.178643006363852</v>
+        <v>-0.1786430063638527</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7546496597609216</v>
+        <v>-0.7546496597609218</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1408728312684805</v>
+        <v>0.1408728312684801</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0425490644298132</v>
+        <v>0.04254906442981315</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03516615546246998</v>
+        <v>0.03516615546246964</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02062022966302016</v>
+        <v>0.02062022966302</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04464040379296103</v>
+        <v>0.04464040379296101</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.03422014791539414</v>
+        <v>-0.03422014791539431</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.05748386225819532</v>
+        <v>-0.05748386225819563</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1379757859546502</v>
+        <v>0.13797578595465</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04216779217079678</v>
+        <v>0.04216779217079671</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.05416142123320938</v>
+        <v>-0.05416142123320929</v>
       </c>
       <c r="Q7" t="n">
         <v>0.1587295074282933</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.007967042644491586</v>
+        <v>-0.007967042644491705</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1206967466031305</v>
+        <v>-0.1206967466031308</v>
       </c>
       <c r="T7" t="n">
         <v>0.1036397952994143</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01600331552649324</v>
+        <v>0.01600331552649308</v>
       </c>
       <c r="V7" t="n">
-        <v>0.05862840242738766</v>
+        <v>0.0586284024273875</v>
       </c>
       <c r="W7" t="n">
-        <v>0.09166700247310913</v>
+        <v>0.09166700247310897</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.04194158433367158</v>
+        <v>-0.04194158433367155</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1060501147009504</v>
+        <v>0.1060501147009502</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1489166461384146</v>
+        <v>0.1489166461384144</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.09367131907232452</v>
+        <v>0.09367131907232409</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.04977427795851627</v>
+        <v>0.0497742779585161</v>
       </c>
     </row>
     <row r="8">
@@ -6518,22 +6518,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1710652621306598</v>
+        <v>0.1710652621306597</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.06978533421626083</v>
+        <v>-0.0697853342162609</v>
       </c>
       <c r="D8" t="n">
         <v>0.1213211475399735</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03367896378764351</v>
+        <v>0.03367896378764345</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.08723230026681918</v>
+        <v>-0.08723230026681925</v>
       </c>
       <c r="G8" t="n">
-        <v>0.16647173257533</v>
+        <v>0.1664717325753297</v>
       </c>
       <c r="H8" t="n">
         <v>0.1387740821352376</v>
@@ -6542,19 +6542,19 @@
         <v>0.1365633062820852</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1325833241121193</v>
+        <v>0.1325833241121194</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1391782634878792</v>
+        <v>0.1391782634878794</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1164579213224304</v>
+        <v>0.1164579213224303</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1103321741293538</v>
+        <v>0.1103321741293537</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1657149746331905</v>
+        <v>0.1657149746331903</v>
       </c>
       <c r="O8" t="n">
         <v>0.1381234840837115</v>
@@ -6566,37 +6566,37 @@
         <v>0.1716355193588777</v>
       </c>
       <c r="R8" t="n">
-        <v>0.124381423036643</v>
+        <v>0.1243814230366431</v>
       </c>
       <c r="S8" t="n">
-        <v>0.09157648433055829</v>
+        <v>0.09157648433055805</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1559913510796427</v>
+        <v>0.1559913510796425</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1307868902416395</v>
+        <v>0.1307868902416392</v>
       </c>
       <c r="V8" t="n">
         <v>0.1704180549124004</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1524675296035037</v>
+        <v>0.1524675296035035</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1145606908171424</v>
+        <v>0.114560690817142</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1565948273413404</v>
+        <v>0.1565948273413401</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1687816280437469</v>
+        <v>0.1687816280437468</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.1530516336799941</v>
+        <v>0.1530516336799937</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1406751810685241</v>
+        <v>0.1406751810685237</v>
       </c>
     </row>
   </sheetData>
@@ -6762,64 +6762,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2109157200167183</v>
+        <v>0.2109157200167186</v>
       </c>
       <c r="C2" t="n">
-        <v>0.405436760310209</v>
+        <v>0.4054367603102088</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3379914426919832</v>
+        <v>0.3379914426919833</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3753236232250849</v>
+        <v>0.3753236232250857</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4245211421462599</v>
+        <v>0.4245211421462594</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2244684605228717</v>
+        <v>0.2244684605228721</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2381484977272511</v>
+        <v>0.2381484977272509</v>
       </c>
       <c r="I2" t="n">
         <v>0.301015168898749</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2461009673569628</v>
+        <v>0.2461009673569629</v>
       </c>
       <c r="K2" t="n">
         <v>0.2621227715276963</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2663287757271048</v>
+        <v>0.2663287757271052</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2467308894423508</v>
+        <v>0.2467308894423507</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2124790617376293</v>
+        <v>0.2124790617376298</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2254730227706084</v>
+        <v>0.2254730227706085</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2372833318364444</v>
+        <v>0.2372833318364445</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2109229980279095</v>
+        <v>0.2109229980279093</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2722427824348688</v>
+        <v>0.2722427824348686</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2751489983612247</v>
+        <v>0.2751489983612246</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2165293483932069</v>
+        <v>0.2165293483932068</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2467413848545497</v>
+        <v>0.2467413848545504</v>
       </c>
       <c r="V2" t="n">
         <v>0.288515759312463</v>
@@ -6828,19 +6828,19 @@
         <v>0.2384087816810354</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2551984258753043</v>
+        <v>0.2551984258753047</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2253457512251377</v>
+        <v>0.2253457512251376</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2220841400872874</v>
+        <v>0.2220841400872876</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2813217373866407</v>
+        <v>0.2813217373866408</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.23411431343686</v>
+        <v>0.2341143134368599</v>
       </c>
     </row>
     <row r="3">
@@ -6850,85 +6850,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1976588486890768</v>
+        <v>0.1976588486890773</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2054852271855022</v>
+        <v>0.2054852271855026</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2452776769345766</v>
+        <v>0.2452776769345767</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2052083490983012</v>
+        <v>0.2052083490983016</v>
       </c>
     </row>
     <row r="4">
@@ -6938,82 +6938,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.042319154298362</v>
+        <v>2.042319154298421</v>
       </c>
       <c r="C4" t="n">
-        <v>54.98316100872879</v>
+        <v>54.98316100872877</v>
       </c>
       <c r="D4" t="n">
-        <v>38.43573167947363</v>
+        <v>38.43573167947364</v>
       </c>
       <c r="E4" t="n">
-        <v>48.40456477016389</v>
+        <v>48.40456477016388</v>
       </c>
       <c r="F4" t="n">
-        <v>61.98837712630385</v>
+        <v>61.98837712630382</v>
       </c>
       <c r="G4" t="n">
-        <v>5.373788947483447</v>
+        <v>5.37378894748348</v>
       </c>
       <c r="H4" t="n">
-        <v>10.34433283659751</v>
+        <v>10.3443328365975</v>
       </c>
       <c r="I4" t="n">
         <v>27.85674691890646</v>
       </c>
       <c r="J4" t="n">
-        <v>11.26871092126142</v>
+        <v>11.26871092126145</v>
       </c>
       <c r="K4" t="n">
-        <v>15.04884518336863</v>
+        <v>15.04884518336865</v>
       </c>
       <c r="L4" t="n">
-        <v>16.51023923824864</v>
+        <v>16.51023923824884</v>
       </c>
       <c r="M4" t="n">
-        <v>11.60018423252595</v>
+        <v>11.60018423252598</v>
       </c>
       <c r="N4" t="n">
-        <v>2.631318073533914</v>
+        <v>2.631318073533917</v>
       </c>
       <c r="O4" t="n">
-        <v>5.526544948989341</v>
+        <v>5.52654494898934</v>
       </c>
       <c r="P4" t="n">
-        <v>8.797648562567606</v>
+        <v>8.79764856256762</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.184784735202264</v>
+        <v>2.184784735202276</v>
       </c>
       <c r="R4" t="n">
-        <v>20.17049954110516</v>
+        <v>20.17049954110515</v>
       </c>
       <c r="S4" t="n">
-        <v>17.368490354496</v>
+        <v>17.36849035449601</v>
       </c>
       <c r="T4" t="n">
-        <v>3.852063821901049</v>
+        <v>3.852063821901054</v>
       </c>
       <c r="U4" t="n">
-        <v>11.50964475789414</v>
+        <v>11.50964475789431</v>
       </c>
       <c r="V4" t="n">
-        <v>11.28938259107554</v>
+        <v>11.28938259107557</v>
       </c>
       <c r="W4" t="n">
-        <v>9.644708832386401</v>
+        <v>9.644708832386394</v>
       </c>
       <c r="X4" t="n">
-        <v>14.58097057339588</v>
+        <v>14.58097057339601</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.031296887251375</v>
+        <v>6.031296887251384</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.844285999995247</v>
+        <v>4.844285999995255</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.25290045591548</v>
+        <v>21.25290045591549</v>
       </c>
       <c r="AB4" t="n">
         <v>9.263259840802107</v>
@@ -7026,82 +7026,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5785298852385141</v>
+        <v>0.5785298852385167</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8898062561701218</v>
+        <v>0.889806256170124</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8898062561701218</v>
+        <v>0.889806256170124</v>
       </c>
       <c r="E5" t="n">
-        <v>0.724060770737414</v>
+        <v>0.7240607707374163</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6270231058615746</v>
+        <v>0.6270231058615769</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9543514394565819</v>
+        <v>0.9543514394565841</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8898062561701218</v>
+        <v>0.8898062561701221</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8898062561701218</v>
+        <v>0.889806256170124</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8899788379239779</v>
+        <v>0.88997883792398</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8898062561701218</v>
+        <v>0.889806256170124</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8898062561701218</v>
+        <v>0.889806256170124</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8898062561700268</v>
+        <v>0.8898062561700296</v>
       </c>
       <c r="N5" t="n">
-        <v>2.631318073533914</v>
+        <v>0.6485149932854095</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7148239274012854</v>
+        <v>0.7148239274012876</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6985700054033961</v>
+        <v>0.6985700054033971</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5173569738266592</v>
+        <v>0.5173569738266616</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8898062561701218</v>
+        <v>0.8898062561701223</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8898062561701218</v>
+        <v>0.8898062561701221</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8898062561701218</v>
+        <v>0.889806256170124</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7378942349752623</v>
+        <v>0.7378942349752644</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8054322003072797</v>
+        <v>0.8054322003072792</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8898674308538379</v>
+        <v>0.8898674308538403</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5458860717119191</v>
+        <v>0.5458860717119204</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.199331753079856</v>
+        <v>1.19933175307986</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5727477668434734</v>
+        <v>0.5727477668434759</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.8898062561701218</v>
+        <v>0.8898062561701223</v>
       </c>
       <c r="AB5" t="n">
         <v>1.214960454073916</v>
@@ -7114,43 +7114,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.026594738384808</v>
+        <v>3.02659473838481</v>
       </c>
       <c r="C6" t="n">
-        <v>3.839103635612085</v>
+        <v>3.839103635612087</v>
       </c>
       <c r="D6" t="n">
-        <v>3.839103635612085</v>
+        <v>3.839103635612087</v>
       </c>
       <c r="E6" t="n">
-        <v>3.651579906904033</v>
+        <v>3.651579906904035</v>
       </c>
       <c r="F6" t="n">
-        <v>1.966048854783379</v>
+        <v>1.966048854783381</v>
       </c>
       <c r="G6" t="n">
-        <v>3.839103649403823</v>
+        <v>3.839103649403824</v>
       </c>
       <c r="H6" t="n">
-        <v>3.839103635612085</v>
+        <v>3.839103635612087</v>
       </c>
       <c r="I6" t="n">
-        <v>3.839103635612085</v>
+        <v>3.839103635612087</v>
       </c>
       <c r="J6" t="n">
-        <v>3.839276217365924</v>
+        <v>3.839276217365925</v>
       </c>
       <c r="K6" t="n">
-        <v>3.839103635612085</v>
+        <v>3.839103635612087</v>
       </c>
       <c r="L6" t="n">
-        <v>3.839103635612085</v>
+        <v>3.839103635612087</v>
       </c>
       <c r="M6" t="n">
-        <v>3.839103635612085</v>
+        <v>3.839103635612087</v>
       </c>
       <c r="N6" t="n">
-        <v>2.631318073533914</v>
+        <v>3.839103635612087</v>
       </c>
       <c r="O6" t="n">
         <v>4.108368038626835</v>
@@ -7159,40 +7159,40 @@
         <v>4.166928423482402</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.839103649403823</v>
+        <v>3.839103649403824</v>
       </c>
       <c r="R6" t="n">
-        <v>3.839103635612085</v>
+        <v>3.839103635612087</v>
       </c>
       <c r="S6" t="n">
-        <v>3.839103635612083</v>
+        <v>3.839103635612087</v>
       </c>
       <c r="T6" t="n">
-        <v>3.839103635612085</v>
+        <v>3.839103635612087</v>
       </c>
       <c r="U6" t="n">
-        <v>3.839103635612085</v>
+        <v>3.839103635612087</v>
       </c>
       <c r="V6" t="n">
-        <v>4.777403796190819</v>
+        <v>4.777403796190822</v>
       </c>
       <c r="W6" t="n">
-        <v>3.839103635612085</v>
+        <v>3.839103635612087</v>
       </c>
       <c r="X6" t="n">
-        <v>3.839103635612085</v>
+        <v>3.839103635612087</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.839103635612085</v>
+        <v>3.839103635612087</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.349233027171</v>
+        <v>3.349233027171001</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.839103635612085</v>
+        <v>3.839103635612087</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.839103635612085</v>
+        <v>3.839103635612087</v>
       </c>
     </row>
     <row r="7">
@@ -7202,85 +7202,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1619024424699067</v>
+        <v>0.1619024424699068</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.9782121552169444</v>
+        <v>-0.9782121552169439</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5817780538188909</v>
+        <v>-0.5817780538188912</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8614056399941272</v>
+        <v>-0.861405639994125</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.082314145030634</v>
+        <v>-1.082314145030632</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08134383442044016</v>
+        <v>0.08134383442043898</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004419506273047445</v>
+        <v>0.004419506273047859</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3641203317714081</v>
+        <v>-0.3641203317714082</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.04327763802165691</v>
+        <v>-0.04327763802165678</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1378608367160049</v>
+        <v>-0.1378608367160048</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1654178551720807</v>
+        <v>-0.1654178551720815</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.04625794865110386</v>
+        <v>-0.04625794865110334</v>
       </c>
       <c r="N7" t="n">
-        <v>0.153194880483301</v>
+        <v>0.1531948804833014</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07515688359869732</v>
+        <v>0.07515688359869763</v>
       </c>
       <c r="P7" t="n">
-        <v>0.004640647802788792</v>
+        <v>0.004640647802789083</v>
       </c>
       <c r="Q7" t="n">
         <v>0.1624198173376711</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1950691263307194</v>
+        <v>-0.1950691263307196</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2189184466724597</v>
+        <v>-0.2189184466724602</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1297380432442818</v>
+        <v>0.129738043244282</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.04987491349845832</v>
+        <v>-0.0498749134984625</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.02449711645283908</v>
+        <v>-0.02449711645283866</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.609533083911287e-05</v>
+        <v>-1.609533083933926e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.09710610758358101</v>
+        <v>-0.097106107583582</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.07728874681008956</v>
+        <v>0.07728874681008975</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.09558133437034448</v>
+        <v>0.09558133437034423</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.2529145184891536</v>
+        <v>-0.2529145184891531</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.02672625913860577</v>
+        <v>0.02672625913860632</v>
       </c>
     </row>
     <row r="8">
@@ -7290,85 +7290,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1912113944930631</v>
+        <v>0.1912113944930628</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1330233404906071</v>
+        <v>-0.1330233404906068</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.02008987861219565</v>
+        <v>-0.02008987861219503</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1065540941640425</v>
+        <v>-0.1065540941640419</v>
       </c>
       <c r="F8" t="n">
         <v>-0.1613056957731415</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1681097116116581</v>
+        <v>0.1681097116116578</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1467889343656855</v>
+        <v>0.1467889343656857</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04196880476017653</v>
+        <v>0.04196880476017676</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1329130709274921</v>
+        <v>0.1329130709274919</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1060251986855621</v>
+        <v>0.1060251986855624</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09769267166844776</v>
+        <v>0.09769267166844842</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1323129225908292</v>
+        <v>0.1323129225908293</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1888127677607144</v>
+        <v>0.1888127677607147</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1662991915188597</v>
+        <v>0.1662991915188596</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1460243885756472</v>
+        <v>0.1460243885756473</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1914540797178623</v>
+        <v>0.1914540797178624</v>
       </c>
       <c r="R8" t="n">
-        <v>0.09011525550603747</v>
+        <v>0.09011525550603762</v>
       </c>
       <c r="S8" t="n">
-        <v>0.08216995467362619</v>
+        <v>0.08216995467362609</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1821901187200326</v>
+        <v>0.1821901187200331</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1306776874708994</v>
+        <v>0.1306776874708993</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1657673685999332</v>
+        <v>0.165767368599933</v>
       </c>
       <c r="W8" t="n">
         <v>0.1450310054542776</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1176443846660375</v>
+        <v>0.1176443846660376</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1671419245284161</v>
+        <v>0.1671419245284164</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1722034990254996</v>
+        <v>0.1722034990254998</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.07287437268339478</v>
+        <v>0.07287437268339508</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1529043937165263</v>
+        <v>0.1529043937165265</v>
       </c>
     </row>
   </sheetData>
@@ -7537,79 +7537,79 @@
         <v>0.1982496914534425</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3617406411685304</v>
+        <v>0.3617406411685303</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2601230172445674</v>
+        <v>0.2601230172445676</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3050215124939337</v>
+        <v>0.3050215124939339</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4061065584043949</v>
+        <v>0.4061065584043951</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2130919514481771</v>
+        <v>0.2130919514481773</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2268382981478926</v>
+        <v>0.2268382981478927</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2566105759654589</v>
+        <v>0.2566105759654592</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2374694010938218</v>
+        <v>0.2374694010938217</v>
       </c>
       <c r="K2" t="n">
         <v>0.2427551592841432</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2493318286036403</v>
+        <v>0.2493318286036405</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2783513634244135</v>
+        <v>0.2783513634244131</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2036231625884379</v>
+        <v>0.203623162588438</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2202827629349006</v>
+        <v>0.2202827629349007</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2311808580153872</v>
+        <v>0.2311808580153873</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2015772524308097</v>
+        <v>0.2015772524308099</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2464610515302104</v>
+        <v>0.2464610515302105</v>
       </c>
       <c r="S2" t="n">
         <v>0.2549648224844274</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2098274600234549</v>
+        <v>0.2098274600234546</v>
       </c>
       <c r="U2" t="n">
         <v>0.2333872213711455</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2721536476951225</v>
+        <v>0.2721536476951223</v>
       </c>
       <c r="W2" t="n">
         <v>0.2230175519499292</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2493512379788106</v>
+        <v>0.2493512379788108</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.21379881367573</v>
+        <v>0.2137988136757301</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.206981299499204</v>
+        <v>0.2069812994992039</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2476336616557087</v>
+        <v>0.2476336616557088</v>
       </c>
       <c r="AB2" t="n">
         <v>0.2257986536329812</v>
@@ -7622,85 +7622,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1715445573664152</v>
+        <v>0.1715445573664153</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1975715018440216</v>
+        <v>0.1975715018440215</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2364581131907247</v>
+        <v>0.2364581131907248</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1972862617124942</v>
+        <v>0.197286261712494</v>
       </c>
     </row>
     <row r="4">
@@ -7710,85 +7710,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7771195092026746</v>
+        <v>0.777119509202674</v>
       </c>
       <c r="C4" t="n">
-        <v>40.63984692837115</v>
+        <v>40.63984692837118</v>
       </c>
       <c r="D4" t="n">
-        <v>16.62274206844583</v>
+        <v>16.62274206844585</v>
       </c>
       <c r="E4" t="n">
-        <v>33.93845311762531</v>
+        <v>33.93845311762534</v>
       </c>
       <c r="F4" t="n">
-        <v>53.64810479423155</v>
+        <v>53.64810479423159</v>
       </c>
       <c r="G4" t="n">
-        <v>4.070414828601821</v>
+        <v>4.070414828601825</v>
       </c>
       <c r="H4" t="n">
-        <v>8.749100754997688</v>
+        <v>8.749100754997684</v>
       </c>
       <c r="I4" t="n">
         <v>16.32418503835505</v>
       </c>
       <c r="J4" t="n">
-        <v>10.1236471825653</v>
+        <v>10.12364718256531</v>
       </c>
       <c r="K4" t="n">
         <v>10.99887884956876</v>
       </c>
       <c r="L4" t="n">
-        <v>12.39350455381596</v>
+        <v>12.39350455381597</v>
       </c>
       <c r="M4" t="n">
         <v>19.94753241514027</v>
       </c>
       <c r="N4" t="n">
-        <v>2.193254771195465</v>
+        <v>2.193254771195468</v>
       </c>
       <c r="O4" t="n">
-        <v>5.682677207767916</v>
+        <v>5.682677207767913</v>
       </c>
       <c r="P4" t="n">
-        <v>8.406603177370599</v>
+        <v>8.406603177370602</v>
       </c>
       <c r="Q4" t="n">
         <v>1.601301145648871</v>
       </c>
       <c r="R4" t="n">
-        <v>13.85588476635339</v>
+        <v>13.85588476635341</v>
       </c>
       <c r="S4" t="n">
-        <v>13.31189541051338</v>
+        <v>13.31189541051337</v>
       </c>
       <c r="T4" t="n">
-        <v>3.855740755035941</v>
+        <v>3.855740755035937</v>
       </c>
       <c r="U4" t="n">
-        <v>8.879558831886804</v>
+        <v>8.879558831886801</v>
       </c>
       <c r="V4" t="n">
-        <v>8.657616316065818</v>
+        <v>8.657616316065811</v>
       </c>
       <c r="W4" t="n">
-        <v>7.07634496039987</v>
+        <v>7.076344960399864</v>
       </c>
       <c r="X4" t="n">
-        <v>13.64617995929635</v>
+        <v>13.64617995929634</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.701387651715384</v>
+        <v>4.701387651715382</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.725714739878778</v>
+        <v>2.725714739878779</v>
       </c>
       <c r="AA4" t="n">
         <v>13.31495677332609</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.311992299074024</v>
+        <v>8.31199229907403</v>
       </c>
     </row>
     <row r="5">
@@ -7798,85 +7798,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5321818951964717</v>
+        <v>0.5321818951964725</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8188776941638243</v>
+        <v>0.8188776941638262</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8188776941638243</v>
+        <v>0.8188776941638262</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6662206382200603</v>
+        <v>0.6662206382200608</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5768457499869422</v>
+        <v>0.5768457499869434</v>
       </c>
       <c r="G5" t="n">
-        <v>0.878325935726007</v>
+        <v>0.8783259357260073</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8188776941638243</v>
+        <v>0.8188776941638262</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8188776941638243</v>
+        <v>0.8188776941638262</v>
       </c>
       <c r="J5" t="n">
-        <v>0.819055209871362</v>
+        <v>0.8190552098713622</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8188776941638243</v>
+        <v>0.8188776941638262</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8188776941638246</v>
+        <v>0.8188776941638244</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8188776941638344</v>
+        <v>0.8188776941638362</v>
       </c>
       <c r="N5" t="n">
-        <v>2.193254771195465</v>
+        <v>0.5966404867918356</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6577132010099822</v>
+        <v>0.6577132010099837</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6427428030337679</v>
+        <v>0.6427428030337689</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4758396271993154</v>
+        <v>0.4758396271993161</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8188776941638243</v>
+        <v>0.8188776941638262</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8188776941638243</v>
+        <v>0.8188776941638262</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8188776941638243</v>
+        <v>0.8188776941638262</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6789909836592091</v>
+        <v>0.6789909836592098</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7412815443253021</v>
+        <v>0.7412815443253034</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8189340380622914</v>
+        <v>0.8189340380622929</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5021158668226079</v>
+        <v>0.502115866822609</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.104010950928847</v>
+        <v>1.104010950928848</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.526856373545172</v>
+        <v>0.5268563735451725</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.8188776941638243</v>
+        <v>0.8188776941638262</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.118355429258445</v>
+        <v>1.118355429258446</v>
       </c>
     </row>
     <row r="6">
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.490609130842459</v>
+        <v>2.49060913084246</v>
       </c>
       <c r="C6" t="n">
         <v>3.157007680032968</v>
@@ -7895,13 +7895,13 @@
         <v>3.157007680032968</v>
       </c>
       <c r="E6" t="n">
-        <v>3.003205468127261</v>
+        <v>3.00320546812726</v>
       </c>
       <c r="F6" t="n">
         <v>1.620777392683561</v>
       </c>
       <c r="G6" t="n">
-        <v>3.157007491600993</v>
+        <v>3.157007491600994</v>
       </c>
       <c r="H6" t="n">
         <v>3.157007680032968</v>
@@ -7910,28 +7910,28 @@
         <v>3.157007680032968</v>
       </c>
       <c r="J6" t="n">
-        <v>3.157185195740503</v>
+        <v>3.157185195740504</v>
       </c>
       <c r="K6" t="n">
         <v>3.157007680032968</v>
       </c>
       <c r="L6" t="n">
-        <v>3.15700768003297</v>
+        <v>3.157007680032968</v>
       </c>
       <c r="M6" t="n">
         <v>3.157007680032968</v>
       </c>
       <c r="N6" t="n">
-        <v>2.193254771195465</v>
+        <v>3.157007680032968</v>
       </c>
       <c r="O6" t="n">
-        <v>3.37785103578308</v>
+        <v>3.377851035783079</v>
       </c>
       <c r="P6" t="n">
         <v>3.425880717604145</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.157007491600993</v>
+        <v>3.157007491600994</v>
       </c>
       <c r="R6" t="n">
         <v>3.157007680032968</v>
@@ -7946,7 +7946,7 @@
         <v>3.157007680032968</v>
       </c>
       <c r="V6" t="n">
-        <v>3.926728232531578</v>
+        <v>3.92672823253158</v>
       </c>
       <c r="W6" t="n">
         <v>3.157007680032968</v>
@@ -7974,85 +7974,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1825961191041123</v>
+        <v>0.1825961191041124</v>
       </c>
       <c r="C7" t="n">
         <v>-0.7759561300650394</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1796001393668735</v>
+        <v>-0.1796001393668734</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6242591268789764</v>
+        <v>-0.6242591268789768</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.028690795567723</v>
+        <v>-1.028690795567722</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09435429105133998</v>
+        <v>0.09435429105133988</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01659404826320886</v>
+        <v>0.01659404826320875</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1583586252392277</v>
+        <v>-0.158358625239228</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.04601009631842362</v>
+        <v>-0.04601009631842343</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0782576750107373</v>
+        <v>-0.0782576750107371</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1193000868409793</v>
+        <v>-0.119300086840979</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.284537205145939</v>
+        <v>-0.2845372051459388</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1511545421245895</v>
+        <v>0.1511545421245893</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0513586515502354</v>
+        <v>0.05135865155023548</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.01373403036850968</v>
+        <v>-0.01373403036850955</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1632462983671219</v>
+        <v>0.1632462983671221</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.09840441061537289</v>
+        <v>-0.09840441061537281</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1537244604106767</v>
+        <v>-0.1537244604106766</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1150600149205342</v>
+        <v>0.115060014920534</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.02526024202829891</v>
+        <v>-0.02526024202829914</v>
       </c>
       <c r="V7" t="n">
         <v>0.01195928749752949</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0365345973054254</v>
+        <v>0.03653459730542491</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1168061779548227</v>
+        <v>-0.1168061779548226</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.09111533966876204</v>
+        <v>0.09111533966876191</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1307242662030803</v>
+        <v>0.1307242662030804</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.1085002040317365</v>
+        <v>-0.1085002040317361</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.02149604366471381</v>
+        <v>0.02149604366471375</v>
       </c>
     </row>
     <row r="8">
@@ -8062,85 +8062,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1915656297519226</v>
+        <v>0.1915656297519225</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.08108774862972165</v>
+        <v>-0.08108774862972132</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08863850368775919</v>
+        <v>0.08863850368775913</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.05707169991358586</v>
+        <v>-0.05707169991358552</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1517169096151689</v>
+        <v>-0.1517169096151686</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1662575767726251</v>
+        <v>0.1662575767726253</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1446227651965503</v>
+        <v>0.1446227651965499</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09479101902941918</v>
+        <v>0.09479101902941914</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1266389976814143</v>
+        <v>0.1266389976814145</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1173817899686482</v>
+        <v>0.1173817899686483</v>
       </c>
       <c r="L8" t="n">
         <v>0.1052840311109797</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05912015052354389</v>
+        <v>0.059120150523544</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1826330831628743</v>
+        <v>0.1826330831628742</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1538852352673722</v>
+        <v>0.1538852352673728</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1351659526367616</v>
+        <v>0.1351659526367613</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.186088960629738</v>
+        <v>0.1860889606297386</v>
       </c>
       <c r="R8" t="n">
         <v>0.1119208533107696</v>
       </c>
       <c r="S8" t="n">
-        <v>0.09525382531358452</v>
+        <v>0.09525382531358438</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1724142556936122</v>
+        <v>0.1724142556936119</v>
       </c>
       <c r="U8" t="n">
         <v>0.1321278529554579</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1700059665694094</v>
+        <v>0.1700059665694093</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1498750323595535</v>
+        <v>0.1498750323595541</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1064381769769669</v>
+        <v>0.1064381769769668</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1654907057991788</v>
+        <v>0.1654907057991783</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1766953794219273</v>
+        <v>0.1766953794219271</v>
       </c>
       <c r="AA8" t="n">
         <v>0.108499845258438</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1458135442110559</v>
+        <v>0.145813544211056</v>
       </c>
     </row>
   </sheetData>
